--- a/data/nzd0218/nzd0218.xlsx
+++ b/data/nzd0218/nzd0218.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA352"/>
+  <dimension ref="A1:AA353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30924,7 +30924,7 @@
         <v>339.34</v>
       </c>
       <c r="H351" t="n">
-        <v>327.65</v>
+        <v>335.14</v>
       </c>
       <c r="I351" t="n">
         <v>344.33</v>
@@ -31011,7 +31011,7 @@
         <v>342.58</v>
       </c>
       <c r="H352" t="n">
-        <v>327.65</v>
+        <v>335.14</v>
       </c>
       <c r="I352" t="n">
         <v>348.12</v>
@@ -31068,6 +31068,93 @@
         <v>346.27</v>
       </c>
       <c r="AA352" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:53:47+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>367.7</v>
+      </c>
+      <c r="C353" t="n">
+        <v>368.43</v>
+      </c>
+      <c r="D353" t="n">
+        <v>367.19</v>
+      </c>
+      <c r="E353" t="n">
+        <v>362.82</v>
+      </c>
+      <c r="F353" t="n">
+        <v>359.74</v>
+      </c>
+      <c r="G353" t="n">
+        <v>358.65</v>
+      </c>
+      <c r="H353" t="n">
+        <v>353.06</v>
+      </c>
+      <c r="I353" t="n">
+        <v>362.07</v>
+      </c>
+      <c r="J353" t="n">
+        <v>356.76</v>
+      </c>
+      <c r="K353" t="n">
+        <v>348.86</v>
+      </c>
+      <c r="L353" t="n">
+        <v>340.21</v>
+      </c>
+      <c r="M353" t="n">
+        <v>330.72</v>
+      </c>
+      <c r="N353" t="n">
+        <v>324.04</v>
+      </c>
+      <c r="O353" t="n">
+        <v>325.09</v>
+      </c>
+      <c r="P353" t="n">
+        <v>322.75</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>317.3</v>
+      </c>
+      <c r="R353" t="n">
+        <v>313.53</v>
+      </c>
+      <c r="S353" t="n">
+        <v>315.86</v>
+      </c>
+      <c r="T353" t="n">
+        <v>319.4</v>
+      </c>
+      <c r="U353" t="n">
+        <v>330.58</v>
+      </c>
+      <c r="V353" t="n">
+        <v>340.62</v>
+      </c>
+      <c r="W353" t="n">
+        <v>344.99</v>
+      </c>
+      <c r="X353" t="n">
+        <v>350.52</v>
+      </c>
+      <c r="Y353" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="Z353" t="n">
+        <v>350.63</v>
+      </c>
+      <c r="AA353" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -31084,7 +31171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B360"/>
+  <dimension ref="A1:B361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34687,6 +34774,16 @@
       </c>
       <c r="B360" t="n">
         <v>0.89</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -34855,28 +34952,28 @@
         <v>0.0512</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1260158356023798</v>
+        <v>-0.1135068255940405</v>
       </c>
       <c r="J2" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K2" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007330610743152444</v>
+        <v>0.005937646663033203</v>
       </c>
       <c r="M2" t="n">
-        <v>8.668891224695358</v>
+        <v>8.707292617150339</v>
       </c>
       <c r="N2" t="n">
-        <v>121.9214225278518</v>
+        <v>122.8201676386521</v>
       </c>
       <c r="O2" t="n">
-        <v>11.04180340921952</v>
+        <v>11.08242607187849</v>
       </c>
       <c r="P2" t="n">
-        <v>349.9896318626841</v>
+        <v>349.8677714094835</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34933,28 +35030,28 @@
         <v>0.0444</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08343385773002189</v>
+        <v>-0.06837178156360948</v>
       </c>
       <c r="J3" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K3" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002526647209473154</v>
+        <v>0.001690664307431144</v>
       </c>
       <c r="M3" t="n">
-        <v>10.05969199850555</v>
+        <v>10.09960500969592</v>
       </c>
       <c r="N3" t="n">
-        <v>155.8140615195066</v>
+        <v>157.1766377295762</v>
       </c>
       <c r="O3" t="n">
-        <v>12.48255028107264</v>
+        <v>12.53701071745479</v>
       </c>
       <c r="P3" t="n">
-        <v>345.2977186649199</v>
+        <v>345.1509867151846</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35011,28 +35108,28 @@
         <v>0.0371</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.181253449442674</v>
+        <v>-0.1654041828039489</v>
       </c>
       <c r="J4" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K4" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01114951922962581</v>
+        <v>0.009256901890915992</v>
       </c>
       <c r="M4" t="n">
-        <v>10.26188287563482</v>
+        <v>10.31133229603756</v>
       </c>
       <c r="N4" t="n">
-        <v>165.2008783921156</v>
+        <v>166.730412100166</v>
       </c>
       <c r="O4" t="n">
-        <v>12.85304938106579</v>
+        <v>12.91241310135971</v>
       </c>
       <c r="P4" t="n">
-        <v>345.3237119789778</v>
+        <v>345.1693113658034</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35089,28 +35186,28 @@
         <v>0.0366</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2886856525941134</v>
+        <v>-0.2722050036225969</v>
       </c>
       <c r="J5" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K5" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02654859315134095</v>
+        <v>0.02355135030835809</v>
       </c>
       <c r="M5" t="n">
-        <v>10.28543678220105</v>
+        <v>10.33188302211769</v>
       </c>
       <c r="N5" t="n">
-        <v>173.2560739943384</v>
+        <v>174.9251512175507</v>
       </c>
       <c r="O5" t="n">
-        <v>13.16267731103131</v>
+        <v>13.22592723469892</v>
       </c>
       <c r="P5" t="n">
-        <v>342.7358958824546</v>
+        <v>342.5753444598104</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35167,28 +35264,28 @@
         <v>0.0382</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2181096715369195</v>
+        <v>-0.2048185323893742</v>
       </c>
       <c r="J6" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K6" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0206174706279515</v>
+        <v>0.01815757937585372</v>
       </c>
       <c r="M6" t="n">
-        <v>8.599503529181032</v>
+        <v>8.639277626491277</v>
       </c>
       <c r="N6" t="n">
-        <v>128.1244808859873</v>
+        <v>129.1661733352612</v>
       </c>
       <c r="O6" t="n">
-        <v>11.31920849202749</v>
+        <v>11.36512971044595</v>
       </c>
       <c r="P6" t="n">
-        <v>343.1547681847534</v>
+        <v>343.025288374681</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35245,28 +35342,28 @@
         <v>0.0418</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2630706604627919</v>
+        <v>-0.2506959340013163</v>
       </c>
       <c r="J7" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K7" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03226818538911125</v>
+        <v>0.0292997887108285</v>
       </c>
       <c r="M7" t="n">
-        <v>8.350256077719333</v>
+        <v>8.390212795324578</v>
       </c>
       <c r="N7" t="n">
-        <v>117.6767346868646</v>
+        <v>118.5609496184968</v>
       </c>
       <c r="O7" t="n">
-        <v>10.84789079438324</v>
+        <v>10.88856967734958</v>
       </c>
       <c r="P7" t="n">
-        <v>344.7947686140828</v>
+        <v>344.674216326266</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35323,28 +35420,28 @@
         <v>0.0328</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2586677758513066</v>
+        <v>-0.2409126528530002</v>
       </c>
       <c r="J8" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K8" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02873078762679315</v>
+        <v>0.0251788427721179</v>
       </c>
       <c r="M8" t="n">
-        <v>8.915769188078567</v>
+        <v>8.9018956370538</v>
       </c>
       <c r="N8" t="n">
-        <v>128.245475315468</v>
+        <v>127.9483982468387</v>
       </c>
       <c r="O8" t="n">
-        <v>11.32455188144184</v>
+        <v>11.31142777225045</v>
       </c>
       <c r="P8" t="n">
-        <v>344.7529777286614</v>
+        <v>344.5807534482612</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35401,28 +35498,28 @@
         <v>0.0326</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1855040356602533</v>
+        <v>-0.1763281596707099</v>
       </c>
       <c r="J9" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K9" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02042354263051915</v>
+        <v>0.01848845785490583</v>
       </c>
       <c r="M9" t="n">
-        <v>7.617398318128126</v>
+        <v>7.642086930306928</v>
       </c>
       <c r="N9" t="n">
-        <v>93.82676766229275</v>
+        <v>94.23191857349418</v>
       </c>
       <c r="O9" t="n">
-        <v>9.686421819345508</v>
+        <v>9.70731263396282</v>
       </c>
       <c r="P9" t="n">
-        <v>351.5511247860007</v>
+        <v>351.4616762178179</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35479,28 +35576,28 @@
         <v>0.0306</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2522269914848064</v>
+        <v>-0.2456603552038603</v>
       </c>
       <c r="J10" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K10" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03804841959861549</v>
+        <v>0.03628036929937739</v>
       </c>
       <c r="M10" t="n">
-        <v>7.777568094471681</v>
+        <v>7.788124154871335</v>
       </c>
       <c r="N10" t="n">
-        <v>91.43500176029336</v>
+        <v>91.51854728502379</v>
       </c>
       <c r="O10" t="n">
-        <v>9.562165118857411</v>
+        <v>9.566532667849089</v>
       </c>
       <c r="P10" t="n">
-        <v>352.3858560023438</v>
+        <v>352.3218429082503</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35557,28 +35654,28 @@
         <v>0.0306</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1273520261050849</v>
+        <v>-0.1240318953671468</v>
       </c>
       <c r="J11" t="n">
+        <v>352</v>
+      </c>
+      <c r="K11" t="n">
         <v>351</v>
       </c>
-      <c r="K11" t="n">
-        <v>350</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.01079953181972049</v>
+        <v>0.01031134542663126</v>
       </c>
       <c r="M11" t="n">
-        <v>7.405408087712137</v>
+        <v>7.40142070671378</v>
       </c>
       <c r="N11" t="n">
-        <v>84.45763816262956</v>
+        <v>84.30502790851867</v>
       </c>
       <c r="O11" t="n">
-        <v>9.190083686377919</v>
+        <v>9.181776947220982</v>
       </c>
       <c r="P11" t="n">
-        <v>346.6409582849785</v>
+        <v>346.6086479613738</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35635,28 +35732,28 @@
         <v>0.0328</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.08836283502760695</v>
+        <v>-0.08733876614764366</v>
       </c>
       <c r="J12" t="n">
+        <v>352</v>
+      </c>
+      <c r="K12" t="n">
         <v>351</v>
       </c>
-      <c r="K12" t="n">
-        <v>350</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.006528729215303231</v>
+        <v>0.006423771384269528</v>
       </c>
       <c r="M12" t="n">
-        <v>6.453249505197977</v>
+        <v>6.440351282209901</v>
       </c>
       <c r="N12" t="n">
-        <v>67.54819820143119</v>
+        <v>67.36412615178173</v>
       </c>
       <c r="O12" t="n">
-        <v>8.218771088272941</v>
+        <v>8.207565178040424</v>
       </c>
       <c r="P12" t="n">
-        <v>340.823121150006</v>
+        <v>340.813155278323</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35713,28 +35810,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06999613445721782</v>
+        <v>-0.07208159451476691</v>
       </c>
       <c r="J13" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K13" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004786644589060862</v>
+        <v>0.005107614545850403</v>
       </c>
       <c r="M13" t="n">
-        <v>5.99764962180916</v>
+        <v>5.989348993415987</v>
       </c>
       <c r="N13" t="n">
-        <v>58.0437513652454</v>
+        <v>57.91231329762187</v>
       </c>
       <c r="O13" t="n">
-        <v>7.618644982229149</v>
+        <v>7.61001401428551</v>
       </c>
       <c r="P13" t="n">
-        <v>336.0767383876262</v>
+        <v>336.0970531813341</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35791,28 +35888,28 @@
         <v>0.0363</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.09495604590573543</v>
+        <v>-0.09968228392154277</v>
       </c>
       <c r="J14" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K14" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L14" t="n">
-        <v>0.008386298594006414</v>
+        <v>0.009272369369683231</v>
       </c>
       <c r="M14" t="n">
-        <v>6.108999446119365</v>
+        <v>6.114571512953773</v>
       </c>
       <c r="N14" t="n">
-        <v>60.44811246123441</v>
+        <v>60.45412847718556</v>
       </c>
       <c r="O14" t="n">
-        <v>7.774838420265363</v>
+        <v>7.775225300734736</v>
       </c>
       <c r="P14" t="n">
-        <v>334.4957250987458</v>
+        <v>334.5417672320686</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35869,28 +35966,28 @@
         <v>0.0343</v>
       </c>
       <c r="I15" t="n">
-        <v>0.04832694165125576</v>
+        <v>0.0432314244681577</v>
       </c>
       <c r="J15" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K15" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001383000415949631</v>
+        <v>0.001112543477243655</v>
       </c>
       <c r="M15" t="n">
-        <v>7.869388705280212</v>
+        <v>7.875588324816049</v>
       </c>
       <c r="N15" t="n">
-        <v>95.61379830792221</v>
+        <v>95.54877249839424</v>
       </c>
       <c r="O15" t="n">
-        <v>9.778230837320327</v>
+        <v>9.774905242425332</v>
       </c>
       <c r="P15" t="n">
-        <v>332.3789149363281</v>
+        <v>332.4285545187418</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35947,28 +36044,28 @@
         <v>0.0361</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1352191140959404</v>
+        <v>0.1284937499030896</v>
       </c>
       <c r="J16" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K16" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L16" t="n">
-        <v>0.008862102139780559</v>
+        <v>0.008041385036436921</v>
       </c>
       <c r="M16" t="n">
-        <v>8.348979371536545</v>
+        <v>8.359748579462918</v>
       </c>
       <c r="N16" t="n">
-        <v>115.941471249787</v>
+        <v>115.9720024966873</v>
       </c>
       <c r="O16" t="n">
-        <v>10.76761214242912</v>
+        <v>10.76902978437182</v>
       </c>
       <c r="P16" t="n">
-        <v>330.491131411207</v>
+        <v>330.5566486606083</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36025,28 +36122,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2455130637372798</v>
+        <v>0.236954346757804</v>
       </c>
       <c r="J17" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K17" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02162163394352046</v>
+        <v>0.02023676774612559</v>
       </c>
       <c r="M17" t="n">
-        <v>9.657562713915761</v>
+        <v>9.671831205807903</v>
       </c>
       <c r="N17" t="n">
-        <v>154.6439184495816</v>
+        <v>154.7874704651796</v>
       </c>
       <c r="O17" t="n">
-        <v>12.4355907961617</v>
+        <v>12.44136127862139</v>
       </c>
       <c r="P17" t="n">
-        <v>325.2069735187634</v>
+        <v>325.2903509506497</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36103,28 +36200,28 @@
         <v>0.0329</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3676595585621605</v>
+        <v>0.3577719448656387</v>
       </c>
       <c r="J18" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K18" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04451351542313919</v>
+        <v>0.04234846686434779</v>
       </c>
       <c r="M18" t="n">
-        <v>10.45966557557792</v>
+        <v>10.47885000485956</v>
       </c>
       <c r="N18" t="n">
-        <v>164.509006906741</v>
+        <v>164.8195912219052</v>
       </c>
       <c r="O18" t="n">
-        <v>12.82610645935628</v>
+        <v>12.8382082559018</v>
       </c>
       <c r="P18" t="n">
-        <v>320.4409924195955</v>
+        <v>320.5373157165893</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36181,28 +36278,28 @@
         <v>0.0362</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4145996993339253</v>
+        <v>0.40640009430537</v>
       </c>
       <c r="J19" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K19" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L19" t="n">
-        <v>0.05805688343068194</v>
+        <v>0.05610821978559044</v>
       </c>
       <c r="M19" t="n">
-        <v>10.30596286688968</v>
+        <v>10.31646652232425</v>
       </c>
       <c r="N19" t="n">
-        <v>158.122702023278</v>
+        <v>158.208483516529</v>
       </c>
       <c r="O19" t="n">
-        <v>12.57468496715834</v>
+        <v>12.57809538509424</v>
       </c>
       <c r="P19" t="n">
-        <v>318.6928666400559</v>
+        <v>318.7727456699855</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36259,28 +36356,28 @@
         <v>0.0408</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5208560585513167</v>
+        <v>0.5131273594868275</v>
       </c>
       <c r="J20" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K20" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L20" t="n">
-        <v>0.08600024269392337</v>
+        <v>0.08400299277060697</v>
       </c>
       <c r="M20" t="n">
-        <v>10.37096949745673</v>
+        <v>10.37566981682673</v>
       </c>
       <c r="N20" t="n">
-        <v>163.4734195174165</v>
+        <v>163.4843149238826</v>
       </c>
       <c r="O20" t="n">
-        <v>12.78567243117923</v>
+        <v>12.78609850282261</v>
       </c>
       <c r="P20" t="n">
-        <v>318.6257496820803</v>
+        <v>318.7010412335317</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36337,28 +36434,28 @@
         <v>0.0379</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5019118324356967</v>
+        <v>0.4974494419732991</v>
       </c>
       <c r="J21" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K21" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08444827420520307</v>
+        <v>0.08354374225968775</v>
       </c>
       <c r="M21" t="n">
-        <v>10.0752341289398</v>
+        <v>10.06541659705173</v>
       </c>
       <c r="N21" t="n">
-        <v>154.8503810909964</v>
+        <v>154.5689173180289</v>
       </c>
       <c r="O21" t="n">
-        <v>12.4438893072462</v>
+        <v>12.43257484666909</v>
       </c>
       <c r="P21" t="n">
-        <v>324.8207314009742</v>
+        <v>324.8642031804151</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36415,28 +36512,28 @@
         <v>0.0374</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6063386989161781</v>
+        <v>0.6013289679623246</v>
       </c>
       <c r="J22" t="n">
+        <v>352</v>
+      </c>
+      <c r="K22" t="n">
         <v>351</v>
       </c>
-      <c r="K22" t="n">
-        <v>350</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.1242138777473377</v>
+        <v>0.1230401010708209</v>
       </c>
       <c r="M22" t="n">
-        <v>10.01343919671723</v>
+        <v>10.00167538656708</v>
       </c>
       <c r="N22" t="n">
-        <v>147.1592671796606</v>
+        <v>146.9401945594084</v>
       </c>
       <c r="O22" t="n">
-        <v>12.13092194269094</v>
+        <v>12.1218890672786</v>
       </c>
       <c r="P22" t="n">
-        <v>333.0127364871938</v>
+        <v>333.0615573219019</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36493,28 +36590,28 @@
         <v>0.0309</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4310745570242265</v>
+        <v>0.4260711535815493</v>
       </c>
       <c r="J23" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K23" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L23" t="n">
-        <v>0.07110080619310799</v>
+        <v>0.0699413969000412</v>
       </c>
       <c r="M23" t="n">
-        <v>9.445191522401707</v>
+        <v>9.435196912881979</v>
       </c>
       <c r="N23" t="n">
-        <v>138.0103349877429</v>
+        <v>137.8161891746892</v>
       </c>
       <c r="O23" t="n">
-        <v>11.74778000252571</v>
+        <v>11.73951400930589</v>
       </c>
       <c r="P23" t="n">
-        <v>342.0058138267042</v>
+        <v>342.0545881643803</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -36571,28 +36668,28 @@
         <v>0.0259</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5537901588332191</v>
+        <v>0.5465772360264857</v>
       </c>
       <c r="J24" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K24" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L24" t="n">
-        <v>0.07944945344155219</v>
+        <v>0.07791639763704927</v>
       </c>
       <c r="M24" t="n">
-        <v>11.93988781906725</v>
+        <v>11.93357767291769</v>
       </c>
       <c r="N24" t="n">
-        <v>201.4709791793791</v>
+        <v>201.312604183688</v>
       </c>
       <c r="O24" t="n">
-        <v>14.19404731496197</v>
+        <v>14.1884672950847</v>
       </c>
       <c r="P24" t="n">
-        <v>348.0095597536436</v>
+        <v>348.079826708546</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -36649,28 +36746,28 @@
         <v>0.0383</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6199713442114497</v>
+        <v>0.6158926876088305</v>
       </c>
       <c r="J25" t="n">
+        <v>352</v>
+      </c>
+      <c r="K25" t="n">
         <v>351</v>
       </c>
-      <c r="K25" t="n">
-        <v>350</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.1063063949918944</v>
+        <v>0.1056620843187234</v>
       </c>
       <c r="M25" t="n">
-        <v>11.28438399361651</v>
+        <v>11.2655568723644</v>
       </c>
       <c r="N25" t="n">
-        <v>183.7047230472544</v>
+        <v>183.3141651560496</v>
       </c>
       <c r="O25" t="n">
-        <v>13.55377154327364</v>
+        <v>13.53935615736766</v>
       </c>
       <c r="P25" t="n">
-        <v>345.6759672493521</v>
+        <v>345.7156592750898</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -36727,28 +36824,28 @@
         <v>0.0429</v>
       </c>
       <c r="I26" t="n">
-        <v>0.556730673583415</v>
+        <v>0.5523268247862325</v>
       </c>
       <c r="J26" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K26" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L26" t="n">
-        <v>0.08695441393768877</v>
+        <v>0.08619417922899797</v>
       </c>
       <c r="M26" t="n">
-        <v>11.15054908043729</v>
+        <v>11.13190340311918</v>
       </c>
       <c r="N26" t="n">
-        <v>185.444293979795</v>
+        <v>185.0684573081517</v>
       </c>
       <c r="O26" t="n">
-        <v>13.61779328598415</v>
+        <v>13.60398681667075</v>
       </c>
       <c r="P26" t="n">
-        <v>343.3200519855992</v>
+        <v>343.3629505678625</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -36786,7 +36883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA352"/>
+  <dimension ref="A1:AA353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84713,7 +84810,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>-37.71178217279461,178.530850627879</t>
+          <t>-37.71182279397928,178.5309181904807</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -84850,7 +84947,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>-37.71178217279461,178.530850627879</t>
+          <t>-37.71182279397928,178.5309181904807</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -84944,6 +85041,143 @@
         </is>
       </c>
       <c r="AA352" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-11 21:53:47+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>-37.70870332255545,178.53463133194828</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>-37.70925663442974,178.53406801046864</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-37.70979925847067,178.53348691921718</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-37.71032490350365,178.53287759440266</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-37.71085754028012,178.53227990538656</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-37.71140096525446,178.53170016659502</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-37.711919980930475,178.5310798358765</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-37.712517198154245,178.5305912277784</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-37.71305787737191,178.53000516076543</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-37.71364480678013,178.52948263790938</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>-37.71422853706926,178.52895473000166</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>-37.71480881846829,178.52841836406807</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>-37.71540061286331,178.52791028692354</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>-37.71602908870335,178.5274762614827</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>-37.71666020322869,178.52703666395522</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>-37.71728226794559,178.52658482315064</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>-37.7179074610718,178.52615235252304</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>-37.71855470658528,178.52578306084655</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>-37.71920197321669,178.52542918776308</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>-37.71986948122785,178.52513134144337</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>-37.72053483872186,178.52481156336577</t>
+        </is>
+      </c>
+      <c r="W353" t="inlineStr">
+        <is>
+          <t>-37.72117892319695,178.5244333440126</t>
+        </is>
+      </c>
+      <c r="X353" t="inlineStr">
+        <is>
+          <t>-37.72183270222198,178.5240613590037</t>
+        </is>
+      </c>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>-37.72252611464337,178.5238361700566</t>
+        </is>
+      </c>
+      <c r="Z353" t="inlineStr">
+        <is>
+          <t>-37.7231959098701,178.52352541198425</t>
+        </is>
+      </c>
+      <c r="AA353" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0218/nzd0218.xlsx
+++ b/data/nzd0218/nzd0218.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA353"/>
+  <dimension ref="A1:AA355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31157,6 +31157,180 @@
       <c r="AA353" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:53:44+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>366.48</v>
+      </c>
+      <c r="C354" t="n">
+        <v>367.11</v>
+      </c>
+      <c r="D354" t="n">
+        <v>365.26</v>
+      </c>
+      <c r="E354" t="n">
+        <v>361.95</v>
+      </c>
+      <c r="F354" t="n">
+        <v>358.7</v>
+      </c>
+      <c r="G354" t="n">
+        <v>358.55</v>
+      </c>
+      <c r="H354" t="n">
+        <v>355.14</v>
+      </c>
+      <c r="I354" t="n">
+        <v>361.54</v>
+      </c>
+      <c r="J354" t="n">
+        <v>356.34</v>
+      </c>
+      <c r="K354" t="n">
+        <v>349.08</v>
+      </c>
+      <c r="L354" t="n">
+        <v>338.87</v>
+      </c>
+      <c r="M354" t="n">
+        <v>329.28</v>
+      </c>
+      <c r="N354" t="n">
+        <v>322.91</v>
+      </c>
+      <c r="O354" t="n">
+        <v>323.67</v>
+      </c>
+      <c r="P354" t="n">
+        <v>322.34</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>317.27</v>
+      </c>
+      <c r="R354" t="n">
+        <v>314.93</v>
+      </c>
+      <c r="S354" t="n">
+        <v>316.14</v>
+      </c>
+      <c r="T354" t="n">
+        <v>319.54</v>
+      </c>
+      <c r="U354" t="n">
+        <v>330.43</v>
+      </c>
+      <c r="V354" t="n">
+        <v>341.09</v>
+      </c>
+      <c r="W354" t="n">
+        <v>346.79</v>
+      </c>
+      <c r="X354" t="n">
+        <v>350.52</v>
+      </c>
+      <c r="Y354" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="Z354" t="n">
+        <v>350.63</v>
+      </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>369.52</v>
+      </c>
+      <c r="C355" t="n">
+        <v>370.34</v>
+      </c>
+      <c r="D355" t="n">
+        <v>367.18</v>
+      </c>
+      <c r="E355" t="n">
+        <v>363.39</v>
+      </c>
+      <c r="F355" t="n">
+        <v>361.91</v>
+      </c>
+      <c r="G355" t="n">
+        <v>363.25</v>
+      </c>
+      <c r="H355" t="n">
+        <v>364.82</v>
+      </c>
+      <c r="I355" t="n">
+        <v>368.93</v>
+      </c>
+      <c r="J355" t="n">
+        <v>362.98</v>
+      </c>
+      <c r="K355" t="n">
+        <v>353.19</v>
+      </c>
+      <c r="L355" t="n">
+        <v>342.13</v>
+      </c>
+      <c r="M355" t="n">
+        <v>331.62</v>
+      </c>
+      <c r="N355" t="n">
+        <v>324.65</v>
+      </c>
+      <c r="O355" t="n">
+        <v>324.95</v>
+      </c>
+      <c r="P355" t="n">
+        <v>323.6</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>318.97</v>
+      </c>
+      <c r="R355" t="n">
+        <v>316.74</v>
+      </c>
+      <c r="S355" t="n">
+        <v>318.49</v>
+      </c>
+      <c r="T355" t="n">
+        <v>323.02</v>
+      </c>
+      <c r="U355" t="n">
+        <v>333.16</v>
+      </c>
+      <c r="V355" t="n">
+        <v>344.03</v>
+      </c>
+      <c r="W355" t="n">
+        <v>349.76</v>
+      </c>
+      <c r="X355" t="n">
+        <v>353.47</v>
+      </c>
+      <c r="Y355" t="n">
+        <v>358.4</v>
+      </c>
+      <c r="Z355" t="n">
+        <v>356.1</v>
+      </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -31171,7 +31345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B361"/>
+  <dimension ref="A1:B363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34784,6 +34958,26 @@
       </c>
       <c r="B361" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -34952,28 +35146,28 @@
         <v>0.0512</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1135068255940405</v>
+        <v>-0.08869894373857043</v>
       </c>
       <c r="J2" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K2" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005937646663033203</v>
+        <v>0.00361256342445393</v>
       </c>
       <c r="M2" t="n">
-        <v>8.707292617150339</v>
+        <v>8.784345514810392</v>
       </c>
       <c r="N2" t="n">
-        <v>122.8201676386521</v>
+        <v>124.6148488478032</v>
       </c>
       <c r="O2" t="n">
-        <v>11.08242607187849</v>
+        <v>11.16310211580111</v>
       </c>
       <c r="P2" t="n">
-        <v>349.8677714094835</v>
+        <v>349.6253162110472</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35030,28 +35224,28 @@
         <v>0.0444</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06837178156360948</v>
+        <v>-0.03858314837092344</v>
       </c>
       <c r="J3" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K3" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001690664307431144</v>
+        <v>0.0005344520879210224</v>
       </c>
       <c r="M3" t="n">
-        <v>10.09960500969592</v>
+        <v>10.17769029421081</v>
       </c>
       <c r="N3" t="n">
-        <v>157.1766377295762</v>
+        <v>159.872774832754</v>
       </c>
       <c r="O3" t="n">
-        <v>12.53701071745479</v>
+        <v>12.64408062425869</v>
       </c>
       <c r="P3" t="n">
-        <v>345.1509867151846</v>
+        <v>344.8598564346604</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35108,28 +35302,28 @@
         <v>0.0371</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1654041828039489</v>
+        <v>-0.1355607411442404</v>
       </c>
       <c r="J4" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K4" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009256901890915992</v>
+        <v>0.006192079596792022</v>
       </c>
       <c r="M4" t="n">
-        <v>10.31133229603756</v>
+        <v>10.40318178308695</v>
       </c>
       <c r="N4" t="n">
-        <v>166.730412100166</v>
+        <v>169.3768020685391</v>
       </c>
       <c r="O4" t="n">
-        <v>12.91241310135971</v>
+        <v>13.01448431819483</v>
       </c>
       <c r="P4" t="n">
-        <v>345.1693113658034</v>
+        <v>344.8776555319147</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35186,28 +35380,28 @@
         <v>0.0366</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2722050036225969</v>
+        <v>-0.2401589009513649</v>
       </c>
       <c r="J5" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K5" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02355135030835809</v>
+        <v>0.01826076560679624</v>
       </c>
       <c r="M5" t="n">
-        <v>10.33188302211769</v>
+        <v>10.42325906500941</v>
       </c>
       <c r="N5" t="n">
-        <v>174.9251512175507</v>
+        <v>178.0716065758761</v>
       </c>
       <c r="O5" t="n">
-        <v>13.22592723469892</v>
+        <v>13.34434736417919</v>
       </c>
       <c r="P5" t="n">
-        <v>342.5753444598104</v>
+        <v>342.262167234633</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35264,28 +35458,28 @@
         <v>0.0382</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2048185323893742</v>
+        <v>-0.1781672721892948</v>
       </c>
       <c r="J6" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K6" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01815757937585372</v>
+        <v>0.01369293295075391</v>
       </c>
       <c r="M6" t="n">
-        <v>8.639277626491277</v>
+        <v>8.722292329932268</v>
       </c>
       <c r="N6" t="n">
-        <v>129.1661733352612</v>
+        <v>131.3081436195498</v>
       </c>
       <c r="O6" t="n">
-        <v>11.36512971044595</v>
+        <v>11.45897655201152</v>
       </c>
       <c r="P6" t="n">
-        <v>343.025288374681</v>
+        <v>342.7648176429694</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35342,28 +35536,28 @@
         <v>0.0418</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2506959340013163</v>
+        <v>-0.2238536375909456</v>
       </c>
       <c r="J7" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K7" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0292997887108285</v>
+        <v>0.02326408503320099</v>
       </c>
       <c r="M7" t="n">
-        <v>8.390212795324578</v>
+        <v>8.482127534162853</v>
       </c>
       <c r="N7" t="n">
-        <v>118.5609496184968</v>
+        <v>120.8202219244744</v>
       </c>
       <c r="O7" t="n">
-        <v>10.88856967734958</v>
+        <v>10.99182523171081</v>
       </c>
       <c r="P7" t="n">
-        <v>344.674216326266</v>
+        <v>344.4118670754081</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35420,28 +35614,28 @@
         <v>0.0328</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2409126528530002</v>
+        <v>-0.2153375235590575</v>
       </c>
       <c r="J8" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K8" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0251788427721179</v>
+        <v>0.0200748476139867</v>
       </c>
       <c r="M8" t="n">
-        <v>8.9018956370538</v>
+        <v>8.988704722807201</v>
       </c>
       <c r="N8" t="n">
-        <v>127.9483982468387</v>
+        <v>129.9870874405042</v>
       </c>
       <c r="O8" t="n">
-        <v>11.31142777225045</v>
+        <v>11.40118798373679</v>
       </c>
       <c r="P8" t="n">
-        <v>344.5807534482612</v>
+        <v>344.3307486913849</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35498,28 +35692,28 @@
         <v>0.0326</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1763281596707099</v>
+        <v>-0.1546634554124778</v>
       </c>
       <c r="J9" t="n">
+        <v>354</v>
+      </c>
+      <c r="K9" t="n">
         <v>352</v>
       </c>
-      <c r="K9" t="n">
-        <v>350</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01848845785490583</v>
+        <v>0.01419116230028816</v>
       </c>
       <c r="M9" t="n">
-        <v>7.642086930306928</v>
+        <v>7.709983550899622</v>
       </c>
       <c r="N9" t="n">
-        <v>94.23191857349418</v>
+        <v>95.67008295102647</v>
       </c>
       <c r="O9" t="n">
-        <v>9.70731263396282</v>
+        <v>9.781108472511001</v>
       </c>
       <c r="P9" t="n">
-        <v>351.4616762178179</v>
+        <v>351.2497585556956</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35576,28 +35770,28 @@
         <v>0.0306</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2456603552038603</v>
+        <v>-0.2293934801323835</v>
       </c>
       <c r="J10" t="n">
+        <v>354</v>
+      </c>
+      <c r="K10" t="n">
         <v>352</v>
       </c>
-      <c r="K10" t="n">
-        <v>350</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.03628036929937739</v>
+        <v>0.03183726690765876</v>
       </c>
       <c r="M10" t="n">
-        <v>7.788124154871335</v>
+        <v>7.82522754014739</v>
       </c>
       <c r="N10" t="n">
-        <v>91.51854728502379</v>
+        <v>92.12992471629022</v>
       </c>
       <c r="O10" t="n">
-        <v>9.566532667849089</v>
+        <v>9.598433451157028</v>
       </c>
       <c r="P10" t="n">
-        <v>352.3218429082503</v>
+        <v>352.1627166250638</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35654,28 +35848,28 @@
         <v>0.0306</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1240318953671468</v>
+        <v>-0.1148580779299202</v>
       </c>
       <c r="J11" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K11" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01031134542663126</v>
+        <v>0.008942189154555691</v>
       </c>
       <c r="M11" t="n">
-        <v>7.40142070671378</v>
+        <v>7.406192353218963</v>
       </c>
       <c r="N11" t="n">
-        <v>84.30502790851867</v>
+        <v>84.19074233864214</v>
       </c>
       <c r="O11" t="n">
-        <v>9.181776947220982</v>
+        <v>9.175551337039217</v>
       </c>
       <c r="P11" t="n">
-        <v>346.6086479613738</v>
+        <v>346.5190582930277</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35732,28 +35926,28 @@
         <v>0.0328</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.08733876614764366</v>
+        <v>-0.0849808254824059</v>
       </c>
       <c r="J12" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K12" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L12" t="n">
-        <v>0.006423771384269528</v>
+        <v>0.006166486579719188</v>
       </c>
       <c r="M12" t="n">
-        <v>6.440351282209901</v>
+        <v>6.416451873333705</v>
       </c>
       <c r="N12" t="n">
-        <v>67.36412615178173</v>
+        <v>67.01991172333058</v>
       </c>
       <c r="O12" t="n">
-        <v>8.207565178040424</v>
+        <v>8.186568983605438</v>
       </c>
       <c r="P12" t="n">
-        <v>340.813155278323</v>
+        <v>340.7901108775163</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35810,28 +36004,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.07208159451476691</v>
+        <v>-0.07646072771306379</v>
       </c>
       <c r="J13" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K13" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005107614545850403</v>
+        <v>0.005816039807724493</v>
       </c>
       <c r="M13" t="n">
-        <v>5.989348993415987</v>
+        <v>5.974057931387469</v>
       </c>
       <c r="N13" t="n">
-        <v>57.91231329762187</v>
+        <v>57.66810251244334</v>
       </c>
       <c r="O13" t="n">
-        <v>7.61001401428551</v>
+        <v>7.593951705959378</v>
       </c>
       <c r="P13" t="n">
-        <v>336.0970531813341</v>
+        <v>336.1398277668828</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35888,28 +36082,28 @@
         <v>0.0363</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.09968228392154277</v>
+        <v>-0.1092086190697265</v>
       </c>
       <c r="J14" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K14" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L14" t="n">
-        <v>0.009272369369683231</v>
+        <v>0.01119735716094128</v>
       </c>
       <c r="M14" t="n">
-        <v>6.114571512953773</v>
+        <v>6.125718890624244</v>
       </c>
       <c r="N14" t="n">
-        <v>60.45412847718556</v>
+        <v>60.48226615880513</v>
       </c>
       <c r="O14" t="n">
-        <v>7.775225300734736</v>
+        <v>7.777034535014303</v>
       </c>
       <c r="P14" t="n">
-        <v>334.5417672320686</v>
+        <v>334.6348484101987</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35966,28 +36160,28 @@
         <v>0.0343</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0432314244681577</v>
+        <v>0.03236481980040928</v>
       </c>
       <c r="J15" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K15" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001112543477243655</v>
+        <v>0.0006295795130374371</v>
       </c>
       <c r="M15" t="n">
-        <v>7.875588324816049</v>
+        <v>7.892939994471776</v>
       </c>
       <c r="N15" t="n">
-        <v>95.54877249839424</v>
+        <v>95.48659936776168</v>
       </c>
       <c r="O15" t="n">
-        <v>9.774905242425332</v>
+        <v>9.771724482800447</v>
       </c>
       <c r="P15" t="n">
-        <v>332.4285545187418</v>
+        <v>332.53473690268</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36044,28 +36238,28 @@
         <v>0.0361</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1284937499030896</v>
+        <v>0.1155979784432569</v>
       </c>
       <c r="J16" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K16" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L16" t="n">
-        <v>0.008041385036436921</v>
+        <v>0.006572676352504025</v>
       </c>
       <c r="M16" t="n">
-        <v>8.359748579462918</v>
+        <v>8.377929597123114</v>
       </c>
       <c r="N16" t="n">
-        <v>115.9720024966873</v>
+        <v>115.988376164031</v>
       </c>
       <c r="O16" t="n">
-        <v>10.76902978437182</v>
+        <v>10.76978997771224</v>
       </c>
       <c r="P16" t="n">
-        <v>330.5566486606083</v>
+        <v>330.6826610502201</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36122,28 +36316,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>0.236954346757804</v>
+        <v>0.2211758752198813</v>
       </c>
       <c r="J17" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K17" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02023676774612559</v>
+        <v>0.01781089103416955</v>
       </c>
       <c r="M17" t="n">
-        <v>9.671831205807903</v>
+        <v>9.694549100773482</v>
       </c>
       <c r="N17" t="n">
-        <v>154.7874704651796</v>
+        <v>154.919152677934</v>
       </c>
       <c r="O17" t="n">
-        <v>12.44136127862139</v>
+        <v>12.44665226789654</v>
       </c>
       <c r="P17" t="n">
-        <v>325.2903509506497</v>
+        <v>325.4445306409519</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36200,28 +36394,28 @@
         <v>0.0329</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3577719448656387</v>
+        <v>0.3411280750279113</v>
       </c>
       <c r="J18" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K18" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04234846686434779</v>
+        <v>0.03892317535257461</v>
       </c>
       <c r="M18" t="n">
-        <v>10.47885000485956</v>
+        <v>10.50295643750077</v>
       </c>
       <c r="N18" t="n">
-        <v>164.8195912219052</v>
+        <v>165.0079639958099</v>
       </c>
       <c r="O18" t="n">
-        <v>12.8382082559018</v>
+        <v>12.84554257304104</v>
       </c>
       <c r="P18" t="n">
-        <v>320.5373157165893</v>
+        <v>320.6999517101667</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36278,28 +36472,28 @@
         <v>0.0362</v>
       </c>
       <c r="I19" t="n">
-        <v>0.40640009430537</v>
+        <v>0.39205106871601</v>
       </c>
       <c r="J19" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K19" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L19" t="n">
-        <v>0.05610821978559044</v>
+        <v>0.0528623119380951</v>
       </c>
       <c r="M19" t="n">
-        <v>10.31646652232425</v>
+        <v>10.32724134979039</v>
       </c>
       <c r="N19" t="n">
-        <v>158.208483516529</v>
+        <v>158.1511614560912</v>
       </c>
       <c r="O19" t="n">
-        <v>12.57809538509424</v>
+        <v>12.57581653238036</v>
       </c>
       <c r="P19" t="n">
-        <v>318.7727456699855</v>
+        <v>318.9129514495117</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36356,28 +36550,28 @@
         <v>0.0408</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5131273594868275</v>
+        <v>0.5001962556712196</v>
       </c>
       <c r="J20" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K20" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L20" t="n">
-        <v>0.08400299277060697</v>
+        <v>0.08089309149523638</v>
       </c>
       <c r="M20" t="n">
-        <v>10.37566981682673</v>
+        <v>10.3757932595709</v>
       </c>
       <c r="N20" t="n">
-        <v>163.4843149238826</v>
+        <v>163.2509084227509</v>
       </c>
       <c r="O20" t="n">
-        <v>12.78609850282261</v>
+        <v>12.7769678884605</v>
       </c>
       <c r="P20" t="n">
-        <v>318.7010412335317</v>
+        <v>318.8273817584469</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36434,28 +36628,28 @@
         <v>0.0379</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4974494419732991</v>
+        <v>0.490112450856277</v>
       </c>
       <c r="J21" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K21" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08354374225968775</v>
+        <v>0.08224948507608221</v>
       </c>
       <c r="M21" t="n">
-        <v>10.06541659705173</v>
+        <v>10.03909719030304</v>
       </c>
       <c r="N21" t="n">
-        <v>154.5689173180289</v>
+        <v>153.9228360236905</v>
       </c>
       <c r="O21" t="n">
-        <v>12.43257484666909</v>
+        <v>12.40656423123221</v>
       </c>
       <c r="P21" t="n">
-        <v>324.8642031804151</v>
+        <v>324.9358818437991</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36512,28 +36706,28 @@
         <v>0.0374</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6013289679623246</v>
+        <v>0.5937697009485655</v>
       </c>
       <c r="J22" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K22" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1230401010708209</v>
+        <v>0.1216650561431091</v>
       </c>
       <c r="M22" t="n">
-        <v>10.00167538656708</v>
+        <v>9.970172248293371</v>
       </c>
       <c r="N22" t="n">
-        <v>146.9401945594084</v>
+        <v>146.3502899550927</v>
       </c>
       <c r="O22" t="n">
-        <v>12.1218890672786</v>
+        <v>12.097532391157</v>
       </c>
       <c r="P22" t="n">
-        <v>333.0615573219019</v>
+        <v>333.1354330860848</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36590,28 +36784,28 @@
         <v>0.0309</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4260711535815493</v>
+        <v>0.4201168286421086</v>
       </c>
       <c r="J23" t="n">
+        <v>354</v>
+      </c>
+      <c r="K23" t="n">
         <v>352</v>
       </c>
-      <c r="K23" t="n">
-        <v>350</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.0699413969000412</v>
+        <v>0.06896265140594393</v>
       </c>
       <c r="M23" t="n">
-        <v>9.435196912881979</v>
+        <v>9.401954254208436</v>
       </c>
       <c r="N23" t="n">
-        <v>137.8161891746892</v>
+        <v>137.1890037375508</v>
       </c>
       <c r="O23" t="n">
-        <v>11.73951400930589</v>
+        <v>11.71277096751878</v>
       </c>
       <c r="P23" t="n">
-        <v>342.0545881643803</v>
+        <v>342.1127925348708</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -36668,28 +36862,28 @@
         <v>0.0259</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5465772360264857</v>
+        <v>0.5341699083806287</v>
       </c>
       <c r="J24" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K24" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L24" t="n">
-        <v>0.07791639763704927</v>
+        <v>0.07544533616283122</v>
       </c>
       <c r="M24" t="n">
-        <v>11.93357767291769</v>
+        <v>11.91429220705802</v>
       </c>
       <c r="N24" t="n">
-        <v>201.312604183688</v>
+        <v>200.8071490843794</v>
       </c>
       <c r="O24" t="n">
-        <v>14.1884672950847</v>
+        <v>14.17064391918657</v>
       </c>
       <c r="P24" t="n">
-        <v>348.079826708546</v>
+        <v>348.2010528762409</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -36746,28 +36940,28 @@
         <v>0.0383</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6158926876088305</v>
+        <v>0.6097481407760467</v>
       </c>
       <c r="J25" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K25" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1056620843187234</v>
+        <v>0.1050205919008145</v>
       </c>
       <c r="M25" t="n">
-        <v>11.2655568723644</v>
+        <v>11.22170197595892</v>
       </c>
       <c r="N25" t="n">
-        <v>183.3141651560496</v>
+        <v>182.4423529124214</v>
       </c>
       <c r="O25" t="n">
-        <v>13.53935615736766</v>
+        <v>13.50712230315627</v>
       </c>
       <c r="P25" t="n">
-        <v>345.7156592750898</v>
+        <v>345.7756194928486</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -36824,28 +37018,28 @@
         <v>0.0429</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5523268247862325</v>
+        <v>0.5468872753043661</v>
       </c>
       <c r="J26" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K26" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L26" t="n">
-        <v>0.08619417922899797</v>
+        <v>0.08568003810240332</v>
       </c>
       <c r="M26" t="n">
-        <v>11.13190340311918</v>
+        <v>11.08503387491476</v>
       </c>
       <c r="N26" t="n">
-        <v>185.0684573081517</v>
+        <v>184.1762447222327</v>
       </c>
       <c r="O26" t="n">
-        <v>13.60398681667075</v>
+        <v>13.57115487798414</v>
       </c>
       <c r="P26" t="n">
-        <v>343.3629505678625</v>
+        <v>343.4160633839411</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -36883,7 +37077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA353"/>
+  <dimension ref="A1:AA355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85183,6 +85377,280 @@
         </is>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-27 21:53:44+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>-37.708696706257605,178.53462032739458</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>-37.70924947577667,178.53405610383652</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-37.709788791596516,178.53346951018702</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-37.71032018524872,178.53286974677042</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-37.71085190003599,178.53227052426223</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-37.711400422920484,178.531699264559</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-37.71193126154209,178.53109859831528</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-37.712514415599394,178.5305863615983</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-37.71305594766374,178.53000107731657</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>-37.713645708577374,178.52948485275172</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>-37.71422304426361,178.52894123950907</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>-37.71480291570799,178.52840386672665</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>-37.71539598080502,178.527898910459</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>-37.71602348929301,178.5274618258099</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>-37.716658685786605,178.5270324371287</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>-37.71728215946464,178.52658451243636</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>-37.71791252354707,178.5261668526368</t>
+        </is>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>-37.718555719085046,178.52578596089333</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>-37.719202495530126,178.5254306287426</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>-37.71986889926378,178.52512981066897</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>-37.72053667859525,178.52481634990986</t>
+        </is>
+      </c>
+      <c r="W354" t="inlineStr">
+        <is>
+          <t>-37.72118596954834,178.52445167561</t>
+        </is>
+      </c>
+      <c r="X354" t="inlineStr">
+        <is>
+          <t>-37.72183270222198,178.5240613590037</t>
+        </is>
+      </c>
+      <c r="Y354" t="inlineStr">
+        <is>
+          <t>-37.72252611464337,178.5238361700566</t>
+        </is>
+      </c>
+      <c r="Z354" t="inlineStr">
+        <is>
+          <t>-37.7231959098701,178.52352541198425</t>
+        </is>
+      </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:53:48+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>-37.70871319276807,178.53464774858116</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>-37.709266992781316,178.53408523900853</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-37.709799204238166,178.53348682901495</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-37.71032799477378,178.53288273595533</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-37.71086930886364,178.53229947946778</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-37.711425912608725,178.5317416602651</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-37.71198375972752,178.53118591589194</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-37.71255321384342,178.5306542127074</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-37.71308645541222,178.53006563472164</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>-37.713662555781106,178.5295262300431</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>-37.71423640735495,178.5289740596659</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>-37.71481250769248,178.52842742490753</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>-37.71540311335445,178.5279164282014</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>-37.716028536648906,178.52747483824726</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>-37.7166633491447,178.52704542688875</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>-37.71728830671788,178.52660211958028</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>-37.7179190686015,178.5261855992151</t>
+        </is>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>-37.718564216847845,178.52581030057453</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>-37.71921547874354,178.52546644738229</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>-37.71987949100654,178.525157670766</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>-37.72054818758571,178.5248462912756</t>
+        </is>
+      </c>
+      <c r="W355" t="inlineStr">
+        <is>
+          <t>-37.72119759602125,178.5244819227528</t>
+        </is>
+      </c>
+      <c r="X355" t="inlineStr">
+        <is>
+          <t>-37.7218420254316,178.52409260362137</t>
+        </is>
+      </c>
+      <c r="Y355" t="inlineStr">
+        <is>
+          <t>-37.72253355072522,178.52387114415458</t>
+        </is>
+      </c>
+      <c r="Z355" t="inlineStr">
+        <is>
+          <t>-37.7232083185695,178.5235852969889</t>
+        </is>
+      </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0218/nzd0218.xlsx
+++ b/data/nzd0218/nzd0218.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA355"/>
+  <dimension ref="A1:AA357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31329,6 +31329,180 @@
         <v>356.1</v>
       </c>
       <c r="AA355" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:53:39+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>374.68</v>
+      </c>
+      <c r="C356" t="n">
+        <v>374.44</v>
+      </c>
+      <c r="D356" t="n">
+        <v>368.57</v>
+      </c>
+      <c r="E356" t="n">
+        <v>364.28</v>
+      </c>
+      <c r="F356" t="n">
+        <v>368.95</v>
+      </c>
+      <c r="G356" t="n">
+        <v>368.15</v>
+      </c>
+      <c r="H356" t="n">
+        <v>370.82</v>
+      </c>
+      <c r="I356" t="n">
+        <v>375.04</v>
+      </c>
+      <c r="J356" t="n">
+        <v>368.71</v>
+      </c>
+      <c r="K356" t="n">
+        <v>358.49</v>
+      </c>
+      <c r="L356" t="n">
+        <v>348.12</v>
+      </c>
+      <c r="M356" t="n">
+        <v>337.53</v>
+      </c>
+      <c r="N356" t="n">
+        <v>330.83</v>
+      </c>
+      <c r="O356" t="n">
+        <v>330.82</v>
+      </c>
+      <c r="P356" t="n">
+        <v>326.41</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>321.23</v>
+      </c>
+      <c r="R356" t="n">
+        <v>320.54</v>
+      </c>
+      <c r="S356" t="n">
+        <v>322.13</v>
+      </c>
+      <c r="T356" t="n">
+        <v>326.52</v>
+      </c>
+      <c r="U356" t="n">
+        <v>337.91</v>
+      </c>
+      <c r="V356" t="n">
+        <v>348.15</v>
+      </c>
+      <c r="W356" t="n">
+        <v>355.53</v>
+      </c>
+      <c r="X356" t="n">
+        <v>358.22</v>
+      </c>
+      <c r="Y356" t="n">
+        <v>365.33</v>
+      </c>
+      <c r="Z356" t="n">
+        <v>365.16</v>
+      </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:53:45+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>373.47</v>
+      </c>
+      <c r="C357" t="n">
+        <v>373.42</v>
+      </c>
+      <c r="D357" t="n">
+        <v>367.71</v>
+      </c>
+      <c r="E357" t="n">
+        <v>362.94</v>
+      </c>
+      <c r="F357" t="n">
+        <v>366.89</v>
+      </c>
+      <c r="G357" t="n">
+        <v>366.68</v>
+      </c>
+      <c r="H357" t="n">
+        <v>368.77</v>
+      </c>
+      <c r="I357" t="n">
+        <v>373.67</v>
+      </c>
+      <c r="J357" t="n">
+        <v>366.93</v>
+      </c>
+      <c r="K357" t="n">
+        <v>358.04</v>
+      </c>
+      <c r="L357" t="n">
+        <v>348.09</v>
+      </c>
+      <c r="M357" t="n">
+        <v>338.09</v>
+      </c>
+      <c r="N357" t="n">
+        <v>331.67</v>
+      </c>
+      <c r="O357" t="n">
+        <v>331.91</v>
+      </c>
+      <c r="P357" t="n">
+        <v>327.47</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>321.59</v>
+      </c>
+      <c r="R357" t="n">
+        <v>321.02</v>
+      </c>
+      <c r="S357" t="n">
+        <v>321.38</v>
+      </c>
+      <c r="T357" t="n">
+        <v>326.87</v>
+      </c>
+      <c r="U357" t="n">
+        <v>337.26</v>
+      </c>
+      <c r="V357" t="n">
+        <v>347.61</v>
+      </c>
+      <c r="W357" t="n">
+        <v>355.88</v>
+      </c>
+      <c r="X357" t="n">
+        <v>359.45</v>
+      </c>
+      <c r="Y357" t="n">
+        <v>365.11</v>
+      </c>
+      <c r="Z357" t="n">
+        <v>365.92</v>
+      </c>
+      <c r="AA357" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31345,7 +31519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B363"/>
+  <dimension ref="A1:B365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34978,6 +35152,26 @@
       </c>
       <c r="B363" t="n">
         <v>0.75</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>0.62</v>
       </c>
     </row>
   </sheetData>
@@ -35146,28 +35340,28 @@
         <v>0.0512</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08869894373857043</v>
+        <v>-0.05769106311368884</v>
       </c>
       <c r="J2" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K2" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00361256342445393</v>
+        <v>0.001504930314414343</v>
       </c>
       <c r="M2" t="n">
-        <v>8.784345514810392</v>
+        <v>8.891196231962287</v>
       </c>
       <c r="N2" t="n">
-        <v>124.6148488478032</v>
+        <v>127.8752216776117</v>
       </c>
       <c r="O2" t="n">
-        <v>11.16310211580111</v>
+        <v>11.30819267954043</v>
       </c>
       <c r="P2" t="n">
-        <v>349.6253162110472</v>
+        <v>349.3214810263282</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35224,28 +35418,28 @@
         <v>0.0444</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03858314837092344</v>
+        <v>-0.003772109521240317</v>
       </c>
       <c r="J3" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K3" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005344520879210224</v>
+        <v>5.025220156773536e-06</v>
       </c>
       <c r="M3" t="n">
-        <v>10.17769029421081</v>
+        <v>10.28207002812565</v>
       </c>
       <c r="N3" t="n">
-        <v>159.872774832754</v>
+        <v>163.9649772547437</v>
       </c>
       <c r="O3" t="n">
-        <v>12.64408062425869</v>
+        <v>12.80488099338466</v>
       </c>
       <c r="P3" t="n">
-        <v>344.8598564346604</v>
+        <v>344.5187545824213</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35302,28 +35496,28 @@
         <v>0.0371</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1355607411442404</v>
+        <v>-0.1044853454271622</v>
       </c>
       <c r="J4" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K4" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006192079596792022</v>
+        <v>0.003653582177858272</v>
       </c>
       <c r="M4" t="n">
-        <v>10.40318178308695</v>
+        <v>10.50004392769213</v>
       </c>
       <c r="N4" t="n">
-        <v>169.3768020685391</v>
+        <v>172.4018930850482</v>
       </c>
       <c r="O4" t="n">
-        <v>13.01448431819483</v>
+        <v>13.1301901389526</v>
       </c>
       <c r="P4" t="n">
-        <v>344.8776555319147</v>
+        <v>344.5731578784363</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35380,28 +35574,28 @@
         <v>0.0366</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2401589009513649</v>
+        <v>-0.208080086901382</v>
       </c>
       <c r="J5" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K5" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01826076560679624</v>
+        <v>0.01363998636126151</v>
       </c>
       <c r="M5" t="n">
-        <v>10.42325906500941</v>
+        <v>10.51953847920342</v>
       </c>
       <c r="N5" t="n">
-        <v>178.0716065758761</v>
+        <v>181.3102447305689</v>
       </c>
       <c r="O5" t="n">
-        <v>13.34434736417919</v>
+        <v>13.46514926506828</v>
       </c>
       <c r="P5" t="n">
-        <v>342.262167234633</v>
+        <v>341.9478385546565</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35458,28 +35652,28 @@
         <v>0.0382</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1781672721892948</v>
+        <v>-0.1435909754931105</v>
       </c>
       <c r="J6" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K6" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01369293295075391</v>
+        <v>0.008734734446361969</v>
       </c>
       <c r="M6" t="n">
-        <v>8.722292329932268</v>
+        <v>8.84853546619466</v>
       </c>
       <c r="N6" t="n">
-        <v>131.3081436195498</v>
+        <v>135.4984275850971</v>
       </c>
       <c r="O6" t="n">
-        <v>11.45897655201152</v>
+        <v>11.64037918562351</v>
       </c>
       <c r="P6" t="n">
-        <v>342.7648176429694</v>
+        <v>342.4260186572486</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35536,28 +35730,28 @@
         <v>0.0418</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2238536375909456</v>
+        <v>-0.1903612503791809</v>
       </c>
       <c r="J7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02326408503320099</v>
+        <v>0.01654125661692174</v>
       </c>
       <c r="M7" t="n">
-        <v>8.482127534162853</v>
+        <v>8.612655130391495</v>
       </c>
       <c r="N7" t="n">
-        <v>120.8202219244744</v>
+        <v>124.7626311656901</v>
       </c>
       <c r="O7" t="n">
-        <v>10.99182523171081</v>
+        <v>11.16971938616589</v>
       </c>
       <c r="P7" t="n">
-        <v>344.4118670754081</v>
+        <v>344.0836874974347</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35614,28 +35808,28 @@
         <v>0.0328</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2153375235590575</v>
+        <v>-0.1792596322981865</v>
       </c>
       <c r="J8" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K8" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0200748476139867</v>
+        <v>0.01363415748364494</v>
       </c>
       <c r="M8" t="n">
-        <v>8.988704722807201</v>
+        <v>9.132195723962235</v>
       </c>
       <c r="N8" t="n">
-        <v>129.9870874405042</v>
+        <v>134.6215237460788</v>
       </c>
       <c r="O8" t="n">
-        <v>11.40118798373679</v>
+        <v>11.60265158255124</v>
       </c>
       <c r="P8" t="n">
-        <v>344.3307486913849</v>
+        <v>343.9772359428653</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35692,28 +35886,28 @@
         <v>0.0326</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1546634554124778</v>
+        <v>-0.1231640809553185</v>
       </c>
       <c r="J9" t="n">
+        <v>356</v>
+      </c>
+      <c r="K9" t="n">
         <v>354</v>
       </c>
-      <c r="K9" t="n">
-        <v>352</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01419116230028816</v>
+        <v>0.008795862586721936</v>
       </c>
       <c r="M9" t="n">
-        <v>7.709983550899622</v>
+        <v>7.831935359378406</v>
       </c>
       <c r="N9" t="n">
-        <v>95.67008295102647</v>
+        <v>99.23642899561074</v>
       </c>
       <c r="O9" t="n">
-        <v>9.781108472511001</v>
+        <v>9.96174829011508</v>
       </c>
       <c r="P9" t="n">
-        <v>351.2497585556956</v>
+        <v>350.9408913980787</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35770,28 +35964,28 @@
         <v>0.0306</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2293934801323835</v>
+        <v>-0.2042149792656096</v>
       </c>
       <c r="J10" t="n">
+        <v>356</v>
+      </c>
+      <c r="K10" t="n">
         <v>354</v>
       </c>
-      <c r="K10" t="n">
-        <v>352</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.03183726690765876</v>
+        <v>0.02504718571406939</v>
       </c>
       <c r="M10" t="n">
-        <v>7.82522754014739</v>
+        <v>7.914053221303059</v>
       </c>
       <c r="N10" t="n">
-        <v>92.12992471629022</v>
+        <v>94.23628723935542</v>
       </c>
       <c r="O10" t="n">
-        <v>9.598433451157028</v>
+        <v>9.70753765067926</v>
       </c>
       <c r="P10" t="n">
-        <v>352.1627166250638</v>
+        <v>351.9158305913766</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35848,28 +36042,28 @@
         <v>0.0306</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1148580779299202</v>
+        <v>-0.09774629961799665</v>
       </c>
       <c r="J11" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K11" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L11" t="n">
-        <v>0.008942189154555691</v>
+        <v>0.006489719520838322</v>
       </c>
       <c r="M11" t="n">
-        <v>7.406192353218963</v>
+        <v>7.452700041718001</v>
       </c>
       <c r="N11" t="n">
-        <v>84.19074233864214</v>
+        <v>84.92622950920644</v>
       </c>
       <c r="O11" t="n">
-        <v>9.175551337039217</v>
+        <v>9.215542822276202</v>
       </c>
       <c r="P11" t="n">
-        <v>346.5190582930277</v>
+        <v>346.3515561764924</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35926,28 +36120,28 @@
         <v>0.0328</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0849808254824059</v>
+        <v>-0.07391038286711794</v>
       </c>
       <c r="J12" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K12" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L12" t="n">
-        <v>0.006166486579719188</v>
+        <v>0.004701348040411446</v>
       </c>
       <c r="M12" t="n">
-        <v>6.416451873333705</v>
+        <v>6.438970507458156</v>
       </c>
       <c r="N12" t="n">
-        <v>67.01991172333058</v>
+        <v>67.14855497787435</v>
       </c>
       <c r="O12" t="n">
-        <v>8.186568983605438</v>
+        <v>8.194422186943649</v>
       </c>
       <c r="P12" t="n">
-        <v>340.7901108775163</v>
+        <v>340.6817448981498</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36004,28 +36198,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.07646072771306379</v>
+        <v>-0.07217458127135847</v>
       </c>
       <c r="J13" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K13" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005816039807724493</v>
+        <v>0.005250915172988924</v>
       </c>
       <c r="M13" t="n">
-        <v>5.974057931387469</v>
+        <v>5.963142273366381</v>
       </c>
       <c r="N13" t="n">
-        <v>57.66810251244334</v>
+        <v>57.41800666322889</v>
       </c>
       <c r="O13" t="n">
-        <v>7.593951705959378</v>
+        <v>7.577467034783384</v>
       </c>
       <c r="P13" t="n">
-        <v>336.1398277668828</v>
+        <v>336.0978274902033</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36082,28 +36276,28 @@
         <v>0.0363</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1092086190697265</v>
+        <v>-0.1097641697471786</v>
       </c>
       <c r="J14" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K14" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01119735716094128</v>
+        <v>0.01146712090661794</v>
       </c>
       <c r="M14" t="n">
-        <v>6.125718890624244</v>
+        <v>6.09394215458767</v>
       </c>
       <c r="N14" t="n">
-        <v>60.48226615880513</v>
+        <v>60.14474691266273</v>
       </c>
       <c r="O14" t="n">
-        <v>7.777034535014303</v>
+        <v>7.755304437136091</v>
       </c>
       <c r="P14" t="n">
-        <v>334.6348484101987</v>
+        <v>334.6402899366765</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36160,28 +36354,28 @@
         <v>0.0343</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03236481980040928</v>
+        <v>0.03001991122093825</v>
       </c>
       <c r="J15" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K15" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0006295795130374371</v>
+        <v>0.000549178031209685</v>
       </c>
       <c r="M15" t="n">
-        <v>7.892939994471776</v>
+        <v>7.861832167249474</v>
       </c>
       <c r="N15" t="n">
-        <v>95.48659936776168</v>
+        <v>94.97446632964962</v>
       </c>
       <c r="O15" t="n">
-        <v>9.771724482800447</v>
+        <v>9.74548440713183</v>
       </c>
       <c r="P15" t="n">
-        <v>332.53473690268</v>
+        <v>332.5577112574409</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36238,28 +36432,28 @@
         <v>0.0361</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1155979784432569</v>
+        <v>0.1077130594821379</v>
       </c>
       <c r="J16" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K16" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L16" t="n">
-        <v>0.006572676352504025</v>
+        <v>0.005778606755811877</v>
       </c>
       <c r="M16" t="n">
-        <v>8.377929597123114</v>
+        <v>8.370568636616385</v>
       </c>
       <c r="N16" t="n">
-        <v>115.988376164031</v>
+        <v>115.5943128151391</v>
       </c>
       <c r="O16" t="n">
-        <v>10.76978997771224</v>
+        <v>10.75147956400137</v>
       </c>
       <c r="P16" t="n">
-        <v>330.6826610502201</v>
+        <v>330.759920628</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36316,28 +36510,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2211758752198813</v>
+        <v>0.2097066776126387</v>
       </c>
       <c r="J17" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K17" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01781089103416955</v>
+        <v>0.0162063557363662</v>
       </c>
       <c r="M17" t="n">
-        <v>9.694549100773482</v>
+        <v>9.695884565079162</v>
       </c>
       <c r="N17" t="n">
-        <v>154.919152677934</v>
+        <v>154.5905511390218</v>
       </c>
       <c r="O17" t="n">
-        <v>12.44665226789654</v>
+        <v>12.43344486210566</v>
       </c>
       <c r="P17" t="n">
-        <v>325.4445306409519</v>
+        <v>325.5569134534465</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36394,28 +36588,28 @@
         <v>0.0329</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3411280750279113</v>
+        <v>0.3307313736737476</v>
       </c>
       <c r="J18" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K18" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03892317535257461</v>
+        <v>0.0370722532371629</v>
       </c>
       <c r="M18" t="n">
-        <v>10.50295643750077</v>
+        <v>10.49574909720422</v>
       </c>
       <c r="N18" t="n">
-        <v>165.0079639958099</v>
+        <v>164.5262838758226</v>
       </c>
       <c r="O18" t="n">
-        <v>12.84554257304104</v>
+        <v>12.82677994961411</v>
       </c>
       <c r="P18" t="n">
-        <v>320.6999517101667</v>
+        <v>320.8018250993661</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36472,28 +36666,28 @@
         <v>0.0362</v>
       </c>
       <c r="I19" t="n">
-        <v>0.39205106871601</v>
+        <v>0.3832848593093874</v>
       </c>
       <c r="J19" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K19" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0528623119380951</v>
+        <v>0.05122095200677279</v>
       </c>
       <c r="M19" t="n">
-        <v>10.32724134979039</v>
+        <v>10.31119148905141</v>
       </c>
       <c r="N19" t="n">
-        <v>158.1511614560912</v>
+        <v>157.5798012270778</v>
       </c>
       <c r="O19" t="n">
-        <v>12.57581653238036</v>
+        <v>12.55307935237716</v>
       </c>
       <c r="P19" t="n">
-        <v>318.9129514495117</v>
+        <v>318.9988512414406</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36550,28 +36744,28 @@
         <v>0.0408</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5001962556712196</v>
+        <v>0.4939175657690327</v>
       </c>
       <c r="J20" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K20" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L20" t="n">
-        <v>0.08089309149523638</v>
+        <v>0.0799836097617066</v>
       </c>
       <c r="M20" t="n">
-        <v>10.3757932595709</v>
+        <v>10.34597565207202</v>
       </c>
       <c r="N20" t="n">
-        <v>163.2509084227509</v>
+        <v>162.4962296241194</v>
       </c>
       <c r="O20" t="n">
-        <v>12.7769678884605</v>
+        <v>12.74740089681498</v>
       </c>
       <c r="P20" t="n">
-        <v>318.8273817584469</v>
+        <v>318.8889041657878</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36628,28 +36822,28 @@
         <v>0.0379</v>
       </c>
       <c r="I21" t="n">
-        <v>0.490112450856277</v>
+        <v>0.4896725337532186</v>
       </c>
       <c r="J21" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K21" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08224948507608221</v>
+        <v>0.08317229608867249</v>
       </c>
       <c r="M21" t="n">
-        <v>10.03909719030304</v>
+        <v>9.984504982356189</v>
       </c>
       <c r="N21" t="n">
-        <v>153.9228360236905</v>
+        <v>153.0595060446676</v>
       </c>
       <c r="O21" t="n">
-        <v>12.40656423123221</v>
+        <v>12.37172203230688</v>
       </c>
       <c r="P21" t="n">
-        <v>324.9358818437991</v>
+        <v>324.9401941788344</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36706,28 +36900,28 @@
         <v>0.0374</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5937697009485655</v>
+        <v>0.5925699042239641</v>
       </c>
       <c r="J22" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K22" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1216650561431091</v>
+        <v>0.1227230757113865</v>
       </c>
       <c r="M22" t="n">
-        <v>9.970172248293371</v>
+        <v>9.917993419213262</v>
       </c>
       <c r="N22" t="n">
-        <v>146.3502899550927</v>
+        <v>145.5321420419724</v>
       </c>
       <c r="O22" t="n">
-        <v>12.097532391157</v>
+        <v>12.06367033874734</v>
       </c>
       <c r="P22" t="n">
-        <v>333.1354330860848</v>
+        <v>333.1471953414422</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36784,28 +36978,28 @@
         <v>0.0309</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4201168286421086</v>
+        <v>0.4229217919488114</v>
       </c>
       <c r="J23" t="n">
+        <v>356</v>
+      </c>
+      <c r="K23" t="n">
         <v>354</v>
       </c>
-      <c r="K23" t="n">
-        <v>352</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.06896265140594393</v>
+        <v>0.07071696905609759</v>
       </c>
       <c r="M23" t="n">
-        <v>9.401954254208436</v>
+        <v>9.366228165010702</v>
       </c>
       <c r="N23" t="n">
-        <v>137.1890037375508</v>
+        <v>136.4466295585924</v>
       </c>
       <c r="O23" t="n">
-        <v>11.71277096751878</v>
+        <v>11.68103717820436</v>
       </c>
       <c r="P23" t="n">
-        <v>342.1127925348708</v>
+        <v>342.0852872563496</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -36862,28 +37056,28 @@
         <v>0.0259</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5341699083806287</v>
+        <v>0.5300449210490238</v>
       </c>
       <c r="J24" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K24" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L24" t="n">
-        <v>0.07544533616283122</v>
+        <v>0.07531309738726544</v>
       </c>
       <c r="M24" t="n">
-        <v>11.91429220705802</v>
+        <v>11.86334763380455</v>
       </c>
       <c r="N24" t="n">
-        <v>200.8071490843794</v>
+        <v>199.7511705925828</v>
       </c>
       <c r="O24" t="n">
-        <v>14.17064391918657</v>
+        <v>14.13333543763052</v>
       </c>
       <c r="P24" t="n">
-        <v>348.2010528762409</v>
+        <v>348.2414694336378</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -36940,28 +37134,28 @@
         <v>0.0383</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6097481407760467</v>
+        <v>0.6134933059602931</v>
       </c>
       <c r="J25" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K25" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1050205919008145</v>
+        <v>0.1074786383894648</v>
       </c>
       <c r="M25" t="n">
-        <v>11.22170197595892</v>
+        <v>11.18223626245293</v>
       </c>
       <c r="N25" t="n">
-        <v>182.4423529124214</v>
+        <v>181.4725219177965</v>
       </c>
       <c r="O25" t="n">
-        <v>13.50712230315627</v>
+        <v>13.47117373942585</v>
       </c>
       <c r="P25" t="n">
-        <v>345.7756194928486</v>
+        <v>345.7389595172536</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -37018,28 +37212,28 @@
         <v>0.0429</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5468872753043661</v>
+        <v>0.5556691504028791</v>
       </c>
       <c r="J26" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K26" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L26" t="n">
-        <v>0.08568003810240332</v>
+        <v>0.08919362133016051</v>
       </c>
       <c r="M26" t="n">
-        <v>11.08503387491476</v>
+        <v>11.08039426325934</v>
       </c>
       <c r="N26" t="n">
-        <v>184.1762447222327</v>
+        <v>183.4534395705587</v>
       </c>
       <c r="O26" t="n">
-        <v>13.57115487798414</v>
+        <v>13.54449849830398</v>
       </c>
       <c r="P26" t="n">
-        <v>343.4160633839411</v>
+        <v>343.3300101348496</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -37077,7 +37271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA355"/>
+  <dimension ref="A1:AA357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85651,6 +85845,280 @@
         </is>
       </c>
     </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:53:39+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>-37.70874117643335,178.53469429246456</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>-37.70928922797641,178.53412222175396</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-37.70980674255502,178.53349936712766</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-37.71033282149332,178.53289076399454</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-37.71090748894277,178.53236298251943</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>-37.71145248694571,178.53178586007408</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-37.71201629988744,178.53124003841728</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-37.712585291924604,178.53071031157893</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>-37.71311278209687,178.5301213446915</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>-37.713684280861905,178.52957958764665</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>-37.71426096098416,178.52903436421596</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>-37.71483673357877,178.52848692444093</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>-37.71542844617906,178.5279786464154</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>-37.71605168348724,178.52753451249268</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>-37.716673749167775,178.52707439612087</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>-37.717296478944206,178.52662552672865</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>-37.71793280958913,178.52622495668214</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>-37.718577379329126,178.5258480011972</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>-37.71922853656107,178.52550247188785</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>-37.71989791984572,178.52520614531127</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>-37.720564315816745,178.52488824993867</t>
+        </is>
+      </c>
+      <c r="W356" t="inlineStr">
+        <is>
+          <t>-37.72122018345427,178.5245406857455</t>
+        </is>
+      </c>
+      <c r="X356" t="inlineStr">
+        <is>
+          <t>-37.72185703736047,178.52414291276617</t>
+        </is>
+      </c>
+      <c r="Y356" t="inlineStr">
+        <is>
+          <t>-37.722549654452294,178.5239468849555</t>
+        </is>
+      </c>
+      <c r="Z356" t="inlineStr">
+        <is>
+          <t>-37.72322887111599,178.5236844849855</t>
+        </is>
+      </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-08 21:53:45+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>-37.708734614374215,178.53468337810125</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>-37.709283696294996,178.5341130211665</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-37.70980207856059,178.5334916097339</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-37.710325554297384,178.53287867683474</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-37.710896316935084,178.53234440065395</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>-37.71144451464664,178.53177260012814</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-37.712005182002706,178.53122154654926</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-37.71257809929697,178.53069773294078</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-37.71310460382803,178.53010403862356</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>-37.71368243628061,178.52957505728298</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>-37.714260838011135,178.52903406218974</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>-37.714839029092495,178.52849256230044</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>-37.71543188947281,178.52798710326306</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>-37.71605598161878,178.52754559340408</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>-37.71667767230612,178.5270853240182</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>-37.717297780714304,178.5266292553014</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>-37.7179345452918,178.52622992815262</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>-37.71857466728049,178.52584023321077</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>-37.719229842342166,178.52550607433903</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>-37.719895398005875,178.52519951195112</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>-37.72056220192332,178.5248827505013</t>
+        </is>
+      </c>
+      <c r="W357" t="inlineStr">
+        <is>
+          <t>-37.72122155357482,178.5245442502262</t>
+        </is>
+      </c>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>-37.72186092465616,178.52415594018981</t>
+        </is>
+      </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>-37.72254914322366,178.52394448048523</t>
+        </is>
+      </c>
+      <c r="Z357" t="inlineStr">
+        <is>
+          <t>-37.72323059516665,178.52369280539344</t>
+        </is>
+      </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0218/nzd0218.xlsx
+++ b/data/nzd0218/nzd0218.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA357"/>
+  <dimension ref="A1:AA359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31503,6 +31503,180 @@
         <v>365.92</v>
       </c>
       <c r="AA357" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:53:28+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>372.41</v>
+      </c>
+      <c r="C358" t="n">
+        <v>372.15</v>
+      </c>
+      <c r="D358" t="n">
+        <v>366</v>
+      </c>
+      <c r="E358" t="n">
+        <v>360.65</v>
+      </c>
+      <c r="F358" t="n">
+        <v>364.4</v>
+      </c>
+      <c r="G358" t="n">
+        <v>365.11</v>
+      </c>
+      <c r="H358" t="n">
+        <v>366.35</v>
+      </c>
+      <c r="I358" t="n">
+        <v>371.89</v>
+      </c>
+      <c r="J358" t="n">
+        <v>366.43</v>
+      </c>
+      <c r="K358" t="n">
+        <v>357.03</v>
+      </c>
+      <c r="L358" t="n">
+        <v>347.24</v>
+      </c>
+      <c r="M358" t="n">
+        <v>338.26</v>
+      </c>
+      <c r="N358" t="n">
+        <v>332.59</v>
+      </c>
+      <c r="O358" t="n">
+        <v>332.32</v>
+      </c>
+      <c r="P358" t="n">
+        <v>328.45</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>321.5</v>
+      </c>
+      <c r="R358" t="n">
+        <v>320.01</v>
+      </c>
+      <c r="S358" t="n">
+        <v>320.49</v>
+      </c>
+      <c r="T358" t="n">
+        <v>326.13</v>
+      </c>
+      <c r="U358" t="n">
+        <v>335.94</v>
+      </c>
+      <c r="V358" t="n">
+        <v>346.95</v>
+      </c>
+      <c r="W358" t="n">
+        <v>356.57</v>
+      </c>
+      <c r="X358" t="n">
+        <v>360.29</v>
+      </c>
+      <c r="Y358" t="n">
+        <v>366.36</v>
+      </c>
+      <c r="Z358" t="n">
+        <v>366.95</v>
+      </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:53:24+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>367.6</v>
+      </c>
+      <c r="C359" t="n">
+        <v>365.89</v>
+      </c>
+      <c r="D359" t="n">
+        <v>359.96</v>
+      </c>
+      <c r="E359" t="n">
+        <v>353.85</v>
+      </c>
+      <c r="F359" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="G359" t="n">
+        <v>359.04</v>
+      </c>
+      <c r="H359" t="n">
+        <v>359.01</v>
+      </c>
+      <c r="I359" t="n">
+        <v>366.04</v>
+      </c>
+      <c r="J359" t="n">
+        <v>362.03</v>
+      </c>
+      <c r="K359" t="n">
+        <v>353.73</v>
+      </c>
+      <c r="L359" t="n">
+        <v>343.91</v>
+      </c>
+      <c r="M359" t="n">
+        <v>336.54</v>
+      </c>
+      <c r="N359" t="n">
+        <v>332.88</v>
+      </c>
+      <c r="O359" t="n">
+        <v>331.72</v>
+      </c>
+      <c r="P359" t="n">
+        <v>328.05</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>321.72</v>
+      </c>
+      <c r="R359" t="n">
+        <v>320</v>
+      </c>
+      <c r="S359" t="n">
+        <v>320.44</v>
+      </c>
+      <c r="T359" t="n">
+        <v>326.32</v>
+      </c>
+      <c r="U359" t="n">
+        <v>333.86</v>
+      </c>
+      <c r="V359" t="n">
+        <v>346.12</v>
+      </c>
+      <c r="W359" t="n">
+        <v>358.14</v>
+      </c>
+      <c r="X359" t="n">
+        <v>360</v>
+      </c>
+      <c r="Y359" t="n">
+        <v>365.34</v>
+      </c>
+      <c r="Z359" t="n">
+        <v>367.02</v>
+      </c>
+      <c r="AA359" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31519,7 +31693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B365"/>
+  <dimension ref="A1:B367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35172,6 +35346,26 @@
       </c>
       <c r="B365" t="n">
         <v>0.62</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>-0.36</v>
       </c>
     </row>
   </sheetData>
@@ -35340,28 +35534,28 @@
         <v>0.0512</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05769106311368884</v>
+        <v>-0.03230823812242099</v>
       </c>
       <c r="J2" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K2" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001504930314414343</v>
+        <v>0.0004689523971953546</v>
       </c>
       <c r="M2" t="n">
-        <v>8.891196231962287</v>
+        <v>8.969516755820077</v>
       </c>
       <c r="N2" t="n">
-        <v>127.8752216776117</v>
+        <v>129.8984677352998</v>
       </c>
       <c r="O2" t="n">
-        <v>11.30819267954043</v>
+        <v>11.39730089693607</v>
       </c>
       <c r="P2" t="n">
-        <v>349.3214810263282</v>
+        <v>349.0719236085671</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35418,28 +35612,28 @@
         <v>0.0444</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.003772109521240317</v>
+        <v>0.02433252243153446</v>
       </c>
       <c r="J3" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K3" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L3" t="n">
-        <v>5.025220156773536e-06</v>
+        <v>0.0002076757965150389</v>
       </c>
       <c r="M3" t="n">
-        <v>10.28207002812565</v>
+        <v>10.35925996799031</v>
       </c>
       <c r="N3" t="n">
-        <v>163.9649772547437</v>
+        <v>166.4210001227265</v>
       </c>
       <c r="O3" t="n">
-        <v>12.80488099338466</v>
+        <v>12.90042635430033</v>
       </c>
       <c r="P3" t="n">
-        <v>344.5187545824213</v>
+        <v>344.2424491049611</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35496,28 +35690,28 @@
         <v>0.0371</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1044853454271622</v>
+        <v>-0.08027799415924372</v>
       </c>
       <c r="J4" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K4" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003653582177858272</v>
+        <v>0.002158427911486016</v>
       </c>
       <c r="M4" t="n">
-        <v>10.50004392769213</v>
+        <v>10.56772936598233</v>
       </c>
       <c r="N4" t="n">
-        <v>172.4018930850482</v>
+        <v>173.9510360629588</v>
       </c>
       <c r="O4" t="n">
-        <v>13.1301901389526</v>
+        <v>13.18904985444209</v>
       </c>
       <c r="P4" t="n">
-        <v>344.5731578784363</v>
+        <v>344.3351760303401</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35574,28 +35768,28 @@
         <v>0.0366</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.208080086901382</v>
+        <v>-0.1842664266755879</v>
       </c>
       <c r="J5" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K5" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01363998636126151</v>
+        <v>0.01073182408942364</v>
       </c>
       <c r="M5" t="n">
-        <v>10.51953847920342</v>
+        <v>10.5773329049239</v>
       </c>
       <c r="N5" t="n">
-        <v>181.3102447305689</v>
+        <v>182.7438921650875</v>
       </c>
       <c r="O5" t="n">
-        <v>13.46514926506828</v>
+        <v>13.51827992627344</v>
       </c>
       <c r="P5" t="n">
-        <v>341.9478385546565</v>
+        <v>341.713737804727</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35652,28 +35846,28 @@
         <v>0.0382</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1435909754931105</v>
+        <v>-0.1180623375668602</v>
       </c>
       <c r="J6" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K6" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008734734446361969</v>
+        <v>0.005881985964817482</v>
       </c>
       <c r="M6" t="n">
-        <v>8.84853546619466</v>
+        <v>8.931669267931658</v>
       </c>
       <c r="N6" t="n">
-        <v>135.4984275850971</v>
+        <v>137.5455881146166</v>
       </c>
       <c r="O6" t="n">
-        <v>11.64037918562351</v>
+        <v>11.72798312220037</v>
       </c>
       <c r="P6" t="n">
-        <v>342.4260186572486</v>
+        <v>342.1750540618504</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35730,28 +35924,28 @@
         <v>0.0418</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1903612503791809</v>
+        <v>-0.1640151880893009</v>
       </c>
       <c r="J7" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K7" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01654125661692174</v>
+        <v>0.01221317241206687</v>
       </c>
       <c r="M7" t="n">
-        <v>8.612655130391495</v>
+        <v>8.711019082456355</v>
       </c>
       <c r="N7" t="n">
-        <v>124.7626311656901</v>
+        <v>127.0319089678379</v>
       </c>
       <c r="O7" t="n">
-        <v>11.16971938616589</v>
+        <v>11.27084331218556</v>
       </c>
       <c r="P7" t="n">
-        <v>344.0836874974347</v>
+        <v>343.824673328383</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35808,28 +36002,28 @@
         <v>0.0328</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1792596322981865</v>
+        <v>-0.1524407261186078</v>
       </c>
       <c r="J8" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K8" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01363415748364494</v>
+        <v>0.009808865565507197</v>
       </c>
       <c r="M8" t="n">
-        <v>9.132195723962235</v>
+        <v>9.224892481504037</v>
       </c>
       <c r="N8" t="n">
-        <v>134.6215237460788</v>
+        <v>136.9658251323939</v>
       </c>
       <c r="O8" t="n">
-        <v>11.60265158255124</v>
+        <v>11.70323994167401</v>
       </c>
       <c r="P8" t="n">
-        <v>343.9772359428653</v>
+        <v>343.7135880907679</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35886,28 +36080,28 @@
         <v>0.0326</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1231640809553185</v>
+        <v>-0.09881785004750493</v>
       </c>
       <c r="J9" t="n">
+        <v>358</v>
+      </c>
+      <c r="K9" t="n">
         <v>356</v>
       </c>
-      <c r="K9" t="n">
-        <v>354</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.008795862586721936</v>
+        <v>0.005614178583046581</v>
       </c>
       <c r="M9" t="n">
-        <v>7.831935359378406</v>
+        <v>7.920754145916924</v>
       </c>
       <c r="N9" t="n">
-        <v>99.23642899561074</v>
+        <v>101.228080555951</v>
       </c>
       <c r="O9" t="n">
-        <v>9.96174829011508</v>
+        <v>10.06121665386204</v>
       </c>
       <c r="P9" t="n">
-        <v>350.9408913980787</v>
+        <v>350.7013678941272</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35964,28 +36158,28 @@
         <v>0.0306</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2042149792656096</v>
+        <v>-0.1839188464141144</v>
       </c>
       <c r="J10" t="n">
+        <v>358</v>
+      </c>
+      <c r="K10" t="n">
         <v>356</v>
       </c>
-      <c r="K10" t="n">
-        <v>354</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.02504718571406939</v>
+        <v>0.02031536591075478</v>
       </c>
       <c r="M10" t="n">
-        <v>7.914053221303059</v>
+        <v>7.982462867085482</v>
       </c>
       <c r="N10" t="n">
-        <v>94.23628723935542</v>
+        <v>95.47191110402417</v>
       </c>
       <c r="O10" t="n">
-        <v>9.70753765067926</v>
+        <v>9.770972884212922</v>
       </c>
       <c r="P10" t="n">
-        <v>351.9158305913766</v>
+        <v>351.7161465575053</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36042,28 +36236,28 @@
         <v>0.0306</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.09774629961799665</v>
+        <v>-0.08446116543444976</v>
       </c>
       <c r="J11" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K11" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L11" t="n">
-        <v>0.006489719520838322</v>
+        <v>0.004877051402988775</v>
       </c>
       <c r="M11" t="n">
-        <v>7.452700041718001</v>
+        <v>7.479912243619395</v>
       </c>
       <c r="N11" t="n">
-        <v>84.92622950920644</v>
+        <v>85.20939681086757</v>
       </c>
       <c r="O11" t="n">
-        <v>9.215542822276202</v>
+        <v>9.23089360846866</v>
       </c>
       <c r="P11" t="n">
-        <v>346.3515561764924</v>
+        <v>346.2210810246772</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36120,28 +36314,28 @@
         <v>0.0328</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.07391038286711794</v>
+        <v>-0.06607416768310884</v>
       </c>
       <c r="J12" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K12" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L12" t="n">
-        <v>0.004701348040411446</v>
+        <v>0.003797400015218333</v>
       </c>
       <c r="M12" t="n">
-        <v>6.438970507458156</v>
+        <v>6.444908881557184</v>
       </c>
       <c r="N12" t="n">
-        <v>67.14855497787435</v>
+        <v>67.04689471338948</v>
       </c>
       <c r="O12" t="n">
-        <v>8.194422186943649</v>
+        <v>8.18821682134697</v>
       </c>
       <c r="P12" t="n">
-        <v>340.6817448981498</v>
+        <v>340.60480215616</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36198,28 +36392,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.07217458127135847</v>
+        <v>-0.06848674259061137</v>
       </c>
       <c r="J13" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K13" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005250915172988924</v>
+        <v>0.004790679498878903</v>
       </c>
       <c r="M13" t="n">
-        <v>5.963142273366381</v>
+        <v>5.949384908259243</v>
       </c>
       <c r="N13" t="n">
-        <v>57.41800666322889</v>
+        <v>57.15626511811815</v>
       </c>
       <c r="O13" t="n">
-        <v>7.577467034783384</v>
+        <v>7.560176262371014</v>
       </c>
       <c r="P13" t="n">
-        <v>336.0978274902033</v>
+        <v>336.0615813620308</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36276,28 +36470,28 @@
         <v>0.0363</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1097641697471786</v>
+        <v>-0.1085970660527373</v>
       </c>
       <c r="J14" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K14" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01146712090661794</v>
+        <v>0.01138067922320951</v>
       </c>
       <c r="M14" t="n">
-        <v>6.09394215458767</v>
+        <v>6.065616782742898</v>
       </c>
       <c r="N14" t="n">
-        <v>60.14474691266273</v>
+        <v>59.81457826506424</v>
       </c>
       <c r="O14" t="n">
-        <v>7.755304437136091</v>
+        <v>7.733988509499109</v>
       </c>
       <c r="P14" t="n">
-        <v>334.6402899366765</v>
+        <v>334.6288085448985</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36354,28 +36548,28 @@
         <v>0.0343</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03001991122093825</v>
+        <v>0.02848674530499302</v>
       </c>
       <c r="J15" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K15" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L15" t="n">
-        <v>0.000549178031209685</v>
+        <v>0.0005013677484564383</v>
       </c>
       <c r="M15" t="n">
-        <v>7.861832167249474</v>
+        <v>7.826455049615088</v>
       </c>
       <c r="N15" t="n">
-        <v>94.97446632964962</v>
+        <v>94.45423289301996</v>
       </c>
       <c r="O15" t="n">
-        <v>9.74548440713183</v>
+        <v>9.718756756551732</v>
       </c>
       <c r="P15" t="n">
-        <v>332.5577112574409</v>
+        <v>332.5727964079766</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36432,28 +36626,28 @@
         <v>0.0361</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1077130594821379</v>
+        <v>0.1015628899238545</v>
       </c>
       <c r="J16" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K16" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L16" t="n">
-        <v>0.005778606755811877</v>
+        <v>0.00520487770911926</v>
       </c>
       <c r="M16" t="n">
-        <v>8.370568636616385</v>
+        <v>8.354671943606849</v>
       </c>
       <c r="N16" t="n">
-        <v>115.5943128151391</v>
+        <v>115.1073793919483</v>
       </c>
       <c r="O16" t="n">
-        <v>10.75147956400137</v>
+        <v>10.72881071656819</v>
       </c>
       <c r="P16" t="n">
-        <v>330.759920628</v>
+        <v>330.8204076456544</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36510,28 +36704,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2097066776126387</v>
+        <v>0.1988066764606119</v>
       </c>
       <c r="J17" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K17" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0162063557363662</v>
+        <v>0.01474231780655844</v>
       </c>
       <c r="M17" t="n">
-        <v>9.695884565079162</v>
+        <v>9.696193720953174</v>
       </c>
       <c r="N17" t="n">
-        <v>154.5905511390218</v>
+        <v>154.2254123755797</v>
       </c>
       <c r="O17" t="n">
-        <v>12.43344486210566</v>
+        <v>12.41875244843779</v>
       </c>
       <c r="P17" t="n">
-        <v>325.5569134534465</v>
+        <v>325.6641032942238</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36588,28 +36782,28 @@
         <v>0.0329</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3307313736737476</v>
+        <v>0.3197445899402689</v>
       </c>
       <c r="J18" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K18" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0370722532371629</v>
+        <v>0.03509588772180372</v>
       </c>
       <c r="M18" t="n">
-        <v>10.49574909720422</v>
+        <v>10.49144332094031</v>
       </c>
       <c r="N18" t="n">
-        <v>164.5262838758226</v>
+        <v>164.1134913197471</v>
       </c>
       <c r="O18" t="n">
-        <v>12.82677994961411</v>
+        <v>12.81067880011622</v>
       </c>
       <c r="P18" t="n">
-        <v>320.8018250993661</v>
+        <v>320.9098715695325</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36666,28 +36860,28 @@
         <v>0.0362</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3832848593093874</v>
+        <v>0.3732776039260836</v>
       </c>
       <c r="J19" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K19" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L19" t="n">
-        <v>0.05122095200677279</v>
+        <v>0.0492288381511119</v>
       </c>
       <c r="M19" t="n">
-        <v>10.31119148905141</v>
+        <v>10.30089760263065</v>
       </c>
       <c r="N19" t="n">
-        <v>157.5798012270778</v>
+        <v>157.1195516923373</v>
       </c>
       <c r="O19" t="n">
-        <v>12.55307935237716</v>
+        <v>12.53473381019068</v>
       </c>
       <c r="P19" t="n">
-        <v>318.9988512414406</v>
+        <v>319.0972654044622</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36744,28 +36938,28 @@
         <v>0.0408</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4939175657690327</v>
+        <v>0.4872485153340488</v>
       </c>
       <c r="J20" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K20" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0799836097617066</v>
+        <v>0.078921629597409</v>
       </c>
       <c r="M20" t="n">
-        <v>10.34597565207202</v>
+        <v>10.31803723671519</v>
       </c>
       <c r="N20" t="n">
-        <v>162.4962296241194</v>
+        <v>161.7750483164845</v>
       </c>
       <c r="O20" t="n">
-        <v>12.74740089681498</v>
+        <v>12.71908205479014</v>
       </c>
       <c r="P20" t="n">
-        <v>318.8889041657878</v>
+        <v>318.9544869308266</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -36822,28 +37016,28 @@
         <v>0.0379</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4896725337532186</v>
+        <v>0.4861276027007098</v>
       </c>
       <c r="J21" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K21" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08317229608867249</v>
+        <v>0.08308878938192543</v>
       </c>
       <c r="M21" t="n">
-        <v>9.984504982356189</v>
+        <v>9.943303791177971</v>
       </c>
       <c r="N21" t="n">
-        <v>153.0595060446676</v>
+        <v>152.2633440052088</v>
       </c>
       <c r="O21" t="n">
-        <v>12.37172203230688</v>
+        <v>12.33950339378408</v>
       </c>
       <c r="P21" t="n">
-        <v>324.9401941788344</v>
+        <v>324.9750829757457</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36900,28 +37094,28 @@
         <v>0.0374</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5925699042239641</v>
+        <v>0.5898050530950752</v>
       </c>
       <c r="J22" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K22" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1227230757113865</v>
+        <v>0.1231786430590608</v>
       </c>
       <c r="M22" t="n">
-        <v>9.917993419213262</v>
+        <v>9.871474209225466</v>
       </c>
       <c r="N22" t="n">
-        <v>145.5321420419724</v>
+        <v>144.7500368865085</v>
       </c>
       <c r="O22" t="n">
-        <v>12.06367033874734</v>
+        <v>12.03121094846685</v>
       </c>
       <c r="P22" t="n">
-        <v>333.1471953414422</v>
+        <v>333.1744071921892</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36978,28 +37172,28 @@
         <v>0.0309</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4229217919488114</v>
+        <v>0.4274872198549635</v>
       </c>
       <c r="J23" t="n">
+        <v>358</v>
+      </c>
+      <c r="K23" t="n">
         <v>356</v>
       </c>
-      <c r="K23" t="n">
-        <v>354</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.07071696905609759</v>
+        <v>0.07302455463184077</v>
       </c>
       <c r="M23" t="n">
-        <v>9.366228165010702</v>
+        <v>9.341584863555251</v>
       </c>
       <c r="N23" t="n">
-        <v>136.4466295585924</v>
+        <v>135.7710212720829</v>
       </c>
       <c r="O23" t="n">
-        <v>11.68103717820436</v>
+        <v>11.65208227194105</v>
       </c>
       <c r="P23" t="n">
-        <v>342.0852872563496</v>
+        <v>342.040337767162</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -37056,28 +37250,28 @@
         <v>0.0259</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5300449210490238</v>
+        <v>0.527499159488106</v>
       </c>
       <c r="J24" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K24" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L24" t="n">
-        <v>0.07531309738726544</v>
+        <v>0.07559606854360934</v>
       </c>
       <c r="M24" t="n">
-        <v>11.86334763380455</v>
+        <v>11.80679429669106</v>
       </c>
       <c r="N24" t="n">
-        <v>199.7511705925828</v>
+        <v>198.6625780821056</v>
       </c>
       <c r="O24" t="n">
-        <v>14.13333543763052</v>
+        <v>14.09477130293733</v>
       </c>
       <c r="P24" t="n">
-        <v>348.2414694336378</v>
+        <v>348.266509334022</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -37134,28 +37328,28 @@
         <v>0.0383</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6134933059602931</v>
+        <v>0.6177781050087749</v>
       </c>
       <c r="J25" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K25" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1074786383894648</v>
+        <v>0.1101252034105454</v>
       </c>
       <c r="M25" t="n">
-        <v>11.18223626245293</v>
+        <v>11.1465747410789</v>
       </c>
       <c r="N25" t="n">
-        <v>181.4725219177965</v>
+        <v>180.5348919189208</v>
       </c>
       <c r="O25" t="n">
-        <v>13.47117373942585</v>
+        <v>13.43632732255808</v>
       </c>
       <c r="P25" t="n">
-        <v>345.7389595172536</v>
+        <v>345.696878221019</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -37212,28 +37406,28 @@
         <v>0.0429</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5556691504028791</v>
+        <v>0.5657709030405199</v>
       </c>
       <c r="J26" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K26" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L26" t="n">
-        <v>0.08919362133016051</v>
+        <v>0.09312462293518908</v>
       </c>
       <c r="M26" t="n">
-        <v>11.08039426325934</v>
+        <v>11.08459018465095</v>
       </c>
       <c r="N26" t="n">
-        <v>183.4534395705587</v>
+        <v>182.8511951530316</v>
       </c>
       <c r="O26" t="n">
-        <v>13.54449849830398</v>
+        <v>13.52224815454263</v>
       </c>
       <c r="P26" t="n">
-        <v>343.3300101348496</v>
+        <v>343.230663683693</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -37271,7 +37465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA357"/>
+  <dimension ref="A1:AA359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86119,6 +86313,280 @@
         </is>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-16 21:53:28+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>-37.70872886579252,178.53467381675972</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>-37.70927680880813,178.53410156553494</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>-37.709792804802504,178.5334761851514</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-37.7103131349816,178.5328580204252</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>-37.71088281290185,178.53232194005687</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>-37.711436000012384,178.53175843814813</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-37.711992057471036,178.53119971713153</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-37.71256875412882,178.53068138989622</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>-37.713102306560984,178.53009917736915</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>-37.71367829621967,178.5295648891341</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>-37.714257353775324,178.52902550478058</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>-37.71483972594482,178.5284942737936</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>-37.7154356606985,178.52799636552564</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>-37.71605759834687,178.5275497614536</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>-37.71668129935759,178.52709542716948</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>-37.71729745527179,178.5266283231582</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>-37.717930893083825,178.52621946735042</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>-37.71857144898205,178.52583101520085</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>-37.71922708154773,178.52549845772808</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>-37.719890276729814,178.52518604112873</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>-37.72055961827543,178.5248760289671</t>
+        </is>
+      </c>
+      <c r="W358" t="inlineStr">
+        <is>
+          <t>-37.72122425466926,178.52455127734564</t>
+        </is>
+      </c>
+      <c r="X358" t="inlineStr">
+        <is>
+          <t>-37.72186357939379,178.5241648369676</t>
+        </is>
+      </c>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>-37.72255204793114,178.52395814224863</t>
+        </is>
+      </c>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t>-37.72323293170799,178.52370408173635</t>
+        </is>
+      </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:53:24+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>-37.708702780236,178.53463042993562</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>-37.70924285944458,178.53404509922396</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>-37.70976004835166,178.53342170303043</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-37.710276256639254,178.53279668265498</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>-37.71084539206092,178.53225969988975</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>-37.711403080356895,178.53170368453556</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-37.71195224997854,178.5311335072907</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-37.71253804105782,178.53062767823297</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>-37.71308209060123,178.53005639834282</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>-37.71366476928114,178.52953166647686</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>-37.714243703762534,178.52899197987892</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>-37.714832675437705,178.5284769575115</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>-37.71543684945427,178.52799928515205</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>-37.71605523240328,178.52754366186898</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>-37.71667981892853,178.52709130343416</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>-37.71729825079792,178.5266306017305</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>-37.71793085692335,178.52621936377813</t>
+        </is>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>-37.718571268178756,178.52583049733516</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>-37.7192277904004,178.52550041334436</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>-37.71988220683686,178.52516481438178</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>-37.72055636914187,178.52486757612928</t>
+        </is>
+      </c>
+      <c r="W359" t="inlineStr">
+        <is>
+          <t>-37.72123040063605,178.5245672665902</t>
+        </is>
+      </c>
+      <c r="X359" t="inlineStr">
+        <is>
+          <t>-37.72186266287731,178.52416176546092</t>
+        </is>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>-37.72254967768996,178.52394699424963</t>
+        </is>
+      </c>
+      <c r="Z359" t="inlineStr">
+        <is>
+          <t>-37.72323309050203,178.52370484808978</t>
+        </is>
+      </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0218/nzd0218.xlsx
+++ b/data/nzd0218/nzd0218.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA359"/>
+  <dimension ref="A1:AA360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31679,6 +31679,93 @@
       <c r="AA359" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:53:04+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>367.26</v>
+      </c>
+      <c r="C360" t="n">
+        <v>364.58</v>
+      </c>
+      <c r="D360" t="n">
+        <v>358.66</v>
+      </c>
+      <c r="E360" t="n">
+        <v>351.98</v>
+      </c>
+      <c r="F360" t="n">
+        <v>355.35</v>
+      </c>
+      <c r="G360" t="n">
+        <v>356.9</v>
+      </c>
+      <c r="H360" t="n">
+        <v>357.07</v>
+      </c>
+      <c r="I360" t="n">
+        <v>364.28</v>
+      </c>
+      <c r="J360" t="n">
+        <v>361.05</v>
+      </c>
+      <c r="K360" t="n">
+        <v>353.19</v>
+      </c>
+      <c r="L360" t="n">
+        <v>344.14</v>
+      </c>
+      <c r="M360" t="n">
+        <v>336.29</v>
+      </c>
+      <c r="N360" t="n">
+        <v>332.83</v>
+      </c>
+      <c r="O360" t="n">
+        <v>331.86</v>
+      </c>
+      <c r="P360" t="n">
+        <v>328.54</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>322.03</v>
+      </c>
+      <c r="R360" t="n">
+        <v>320.41</v>
+      </c>
+      <c r="S360" t="n">
+        <v>321.51</v>
+      </c>
+      <c r="T360" t="n">
+        <v>326.81</v>
+      </c>
+      <c r="U360" t="n">
+        <v>334.44</v>
+      </c>
+      <c r="V360" t="n">
+        <v>346.7</v>
+      </c>
+      <c r="W360" t="n">
+        <v>358.91</v>
+      </c>
+      <c r="X360" t="n">
+        <v>360.12</v>
+      </c>
+      <c r="Y360" t="n">
+        <v>362.84</v>
+      </c>
+      <c r="Z360" t="n">
+        <v>364.35</v>
+      </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -31693,7 +31780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B367"/>
+  <dimension ref="A1:B368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35366,6 +35453,16 @@
       </c>
       <c r="B367" t="n">
         <v>-0.36</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>
@@ -35534,28 +35631,28 @@
         <v>0.0512</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03230823812242099</v>
+        <v>-0.02145663805186883</v>
       </c>
       <c r="J2" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K2" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004689523971953546</v>
+        <v>0.0002067182788405564</v>
       </c>
       <c r="M2" t="n">
-        <v>8.969516755820077</v>
+        <v>8.998941142173653</v>
       </c>
       <c r="N2" t="n">
-        <v>129.8984677352998</v>
+        <v>130.538007644981</v>
       </c>
       <c r="O2" t="n">
-        <v>11.39730089693607</v>
+        <v>11.42532308711578</v>
       </c>
       <c r="P2" t="n">
-        <v>349.0719236085671</v>
+        <v>348.9648688882542</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35612,28 +35709,28 @@
         <v>0.0444</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02433252243153446</v>
+        <v>0.03554563856616799</v>
       </c>
       <c r="J3" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K3" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002076757965150389</v>
+        <v>0.00044327847329384</v>
       </c>
       <c r="M3" t="n">
-        <v>10.35925996799031</v>
+        <v>10.38450610420712</v>
       </c>
       <c r="N3" t="n">
-        <v>166.4210001227265</v>
+        <v>167.026637976211</v>
       </c>
       <c r="O3" t="n">
-        <v>12.90042635430033</v>
+        <v>12.92387859646674</v>
       </c>
       <c r="P3" t="n">
-        <v>344.2424491049611</v>
+        <v>344.1318279058913</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35690,28 +35787,28 @@
         <v>0.0371</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08027799415924372</v>
+        <v>-0.0708961144782764</v>
       </c>
       <c r="J4" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K4" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002158427911486016</v>
+        <v>0.001688525848140277</v>
       </c>
       <c r="M4" t="n">
-        <v>10.56772936598233</v>
+        <v>10.58682443354506</v>
       </c>
       <c r="N4" t="n">
-        <v>173.9510360629588</v>
+        <v>174.2149871000956</v>
       </c>
       <c r="O4" t="n">
-        <v>13.18904985444209</v>
+        <v>13.19905250766492</v>
       </c>
       <c r="P4" t="n">
-        <v>344.3351760303401</v>
+        <v>344.2426206008435</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35768,28 +35865,28 @@
         <v>0.0366</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1842664266755879</v>
+        <v>-0.1756134816789424</v>
       </c>
       <c r="J5" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K5" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01073182408942364</v>
+        <v>0.009789920783186856</v>
       </c>
       <c r="M5" t="n">
-        <v>10.5773329049239</v>
+        <v>10.59086389472946</v>
       </c>
       <c r="N5" t="n">
-        <v>182.7438921650875</v>
+        <v>182.8715589268849</v>
       </c>
       <c r="O5" t="n">
-        <v>13.51827992627344</v>
+        <v>13.52300110651792</v>
       </c>
       <c r="P5" t="n">
-        <v>341.713737804727</v>
+        <v>341.6283735634652</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35846,28 +35943,28 @@
         <v>0.0382</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1180623375668602</v>
+        <v>-0.1087604889079304</v>
       </c>
       <c r="J6" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K6" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005881985964817482</v>
+        <v>0.005003655330566015</v>
       </c>
       <c r="M6" t="n">
-        <v>8.931669267931658</v>
+        <v>8.955646482782274</v>
       </c>
       <c r="N6" t="n">
-        <v>137.5455881146166</v>
+        <v>137.8982316652153</v>
       </c>
       <c r="O6" t="n">
-        <v>11.72798312220037</v>
+        <v>11.74300777761879</v>
       </c>
       <c r="P6" t="n">
-        <v>342.1750540618504</v>
+        <v>342.0832881655678</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35924,28 +36021,28 @@
         <v>0.0418</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1640151880893009</v>
+        <v>-0.1540720098598392</v>
       </c>
       <c r="J7" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K7" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01221317241206687</v>
+        <v>0.01079547328524422</v>
       </c>
       <c r="M7" t="n">
-        <v>8.711019082456355</v>
+        <v>8.743758555054537</v>
       </c>
       <c r="N7" t="n">
-        <v>127.0319089678379</v>
+        <v>127.5187948477384</v>
       </c>
       <c r="O7" t="n">
-        <v>11.27084331218556</v>
+        <v>11.2924220098143</v>
       </c>
       <c r="P7" t="n">
-        <v>343.824673328383</v>
+        <v>343.7265804980671</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36002,28 +36099,28 @@
         <v>0.0328</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1524407261186078</v>
+        <v>-0.1425090874371866</v>
       </c>
       <c r="J8" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K8" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009808865565507197</v>
+        <v>0.008589369324087825</v>
       </c>
       <c r="M8" t="n">
-        <v>9.224892481504037</v>
+        <v>9.252889357724872</v>
       </c>
       <c r="N8" t="n">
-        <v>136.9658251323939</v>
+        <v>137.42308963976</v>
       </c>
       <c r="O8" t="n">
-        <v>11.70323994167401</v>
+        <v>11.72275947205947</v>
       </c>
       <c r="P8" t="n">
-        <v>343.7135880907679</v>
+        <v>343.6156091020126</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36080,28 +36177,28 @@
         <v>0.0326</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.09881785004750493</v>
+        <v>-0.08957403108083632</v>
       </c>
       <c r="J9" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K9" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005614178583046581</v>
+        <v>0.004615973520503136</v>
       </c>
       <c r="M9" t="n">
-        <v>7.920754145916924</v>
+        <v>7.950450494152142</v>
       </c>
       <c r="N9" t="n">
-        <v>101.228080555951</v>
+        <v>101.674507505159</v>
       </c>
       <c r="O9" t="n">
-        <v>10.06121665386204</v>
+        <v>10.08337778252699</v>
       </c>
       <c r="P9" t="n">
-        <v>350.7013678941272</v>
+        <v>350.610106140043</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36158,28 +36255,28 @@
         <v>0.0306</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1839188464141144</v>
+        <v>-0.1757976454223021</v>
       </c>
       <c r="J10" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K10" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02031536591075478</v>
+        <v>0.01861091571893425</v>
       </c>
       <c r="M10" t="n">
-        <v>7.982462867085482</v>
+        <v>8.004982360149002</v>
       </c>
       <c r="N10" t="n">
-        <v>95.47191110402417</v>
+        <v>95.76792322711023</v>
       </c>
       <c r="O10" t="n">
-        <v>9.770972884212922</v>
+        <v>9.786108686659382</v>
       </c>
       <c r="P10" t="n">
-        <v>351.7161465575053</v>
+        <v>351.6359681106474</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36236,28 +36333,28 @@
         <v>0.0306</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08446116543444976</v>
+        <v>-0.0792073540728068</v>
       </c>
       <c r="J11" t="n">
+        <v>359</v>
+      </c>
+      <c r="K11" t="n">
         <v>358</v>
       </c>
-      <c r="K11" t="n">
-        <v>357</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.004877051402988775</v>
+        <v>0.004309249001914317</v>
       </c>
       <c r="M11" t="n">
-        <v>7.479912243619395</v>
+        <v>7.486103854181492</v>
       </c>
       <c r="N11" t="n">
-        <v>85.20939681086757</v>
+        <v>85.20688776372025</v>
       </c>
       <c r="O11" t="n">
-        <v>9.23089360846866</v>
+        <v>9.230757702578931</v>
       </c>
       <c r="P11" t="n">
-        <v>346.2210810246772</v>
+        <v>346.1693015629284</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36314,28 +36411,28 @@
         <v>0.0328</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.06607416768310884</v>
+        <v>-0.06305559149832674</v>
       </c>
       <c r="J12" t="n">
+        <v>359</v>
+      </c>
+      <c r="K12" t="n">
         <v>358</v>
       </c>
-      <c r="K12" t="n">
-        <v>357</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.003797400015218333</v>
+        <v>0.003479251415790752</v>
       </c>
       <c r="M12" t="n">
-        <v>6.444908881557184</v>
+        <v>6.443409829899355</v>
       </c>
       <c r="N12" t="n">
-        <v>67.04689471338948</v>
+        <v>66.93735517996183</v>
       </c>
       <c r="O12" t="n">
-        <v>8.18821682134697</v>
+        <v>8.181525235551243</v>
       </c>
       <c r="P12" t="n">
-        <v>340.60480215616</v>
+        <v>340.5750522775791</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36392,28 +36489,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06848674259061137</v>
+        <v>-0.06731415792549397</v>
       </c>
       <c r="J13" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K13" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004790679498878903</v>
+        <v>0.00465950419019856</v>
       </c>
       <c r="M13" t="n">
-        <v>5.949384908259243</v>
+        <v>5.938916082615866</v>
       </c>
       <c r="N13" t="n">
-        <v>57.15626511811815</v>
+        <v>57.00749373316</v>
       </c>
       <c r="O13" t="n">
-        <v>7.560176262371014</v>
+        <v>7.550330703562593</v>
       </c>
       <c r="P13" t="n">
-        <v>336.0615813620308</v>
+        <v>336.0500125380709</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36470,28 +36567,28 @@
         <v>0.0363</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1085970660527373</v>
+        <v>-0.1079674362534236</v>
       </c>
       <c r="J14" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K14" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01138067922320951</v>
+        <v>0.01132662557928177</v>
       </c>
       <c r="M14" t="n">
-        <v>6.065616782742898</v>
+        <v>6.051778962068178</v>
       </c>
       <c r="N14" t="n">
-        <v>59.81457826506424</v>
+        <v>59.65133500069717</v>
       </c>
       <c r="O14" t="n">
-        <v>7.733988509499109</v>
+        <v>7.723427671746346</v>
       </c>
       <c r="P14" t="n">
-        <v>334.6288085448985</v>
+        <v>334.622597033082</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36548,28 +36645,28 @@
         <v>0.0343</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02848674530499302</v>
+        <v>0.02764873361801335</v>
       </c>
       <c r="J15" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K15" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0005013677484564383</v>
+        <v>0.0004755417730316625</v>
       </c>
       <c r="M15" t="n">
-        <v>7.826455049615088</v>
+        <v>7.809290386303483</v>
       </c>
       <c r="N15" t="n">
-        <v>94.45423289301996</v>
+        <v>94.19710103087425</v>
       </c>
       <c r="O15" t="n">
-        <v>9.718756756551732</v>
+        <v>9.705519101566605</v>
       </c>
       <c r="P15" t="n">
-        <v>332.5727964079766</v>
+        <v>332.5810636778893</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36626,28 +36723,28 @@
         <v>0.0361</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1015628899238545</v>
+        <v>0.09871635526736977</v>
       </c>
       <c r="J16" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K16" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00520487770911926</v>
+        <v>0.004949408729286842</v>
       </c>
       <c r="M16" t="n">
-        <v>8.354671943606849</v>
+        <v>8.345569233875075</v>
       </c>
       <c r="N16" t="n">
-        <v>115.1073793919483</v>
+        <v>114.8556495954663</v>
       </c>
       <c r="O16" t="n">
-        <v>10.72881071656819</v>
+        <v>10.71707280909607</v>
       </c>
       <c r="P16" t="n">
-        <v>330.8204076456544</v>
+        <v>330.8484896768323</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36704,28 +36801,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1988066764606119</v>
+        <v>0.1937097604059312</v>
       </c>
       <c r="J17" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K17" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01474231780655844</v>
+        <v>0.01408180379747315</v>
       </c>
       <c r="M17" t="n">
-        <v>9.696193720953174</v>
+        <v>9.694973713310461</v>
       </c>
       <c r="N17" t="n">
-        <v>154.2254123755797</v>
+        <v>154.0167293857898</v>
       </c>
       <c r="O17" t="n">
-        <v>12.41875244843779</v>
+        <v>12.41034767384821</v>
       </c>
       <c r="P17" t="n">
-        <v>325.6641032942238</v>
+        <v>325.7143861022102</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36782,28 +36879,28 @@
         <v>0.0329</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3197445899402689</v>
+        <v>0.3145881562638008</v>
       </c>
       <c r="J18" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K18" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03509588772180372</v>
+        <v>0.03419206585180645</v>
       </c>
       <c r="M18" t="n">
-        <v>10.49144332094031</v>
+        <v>10.48764905176293</v>
       </c>
       <c r="N18" t="n">
-        <v>164.1134913197471</v>
+        <v>163.8824543701753</v>
       </c>
       <c r="O18" t="n">
-        <v>12.81067880011622</v>
+        <v>12.80165826641905</v>
       </c>
       <c r="P18" t="n">
-        <v>320.9098715695325</v>
+        <v>320.9607415390723</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36860,28 +36957,28 @@
         <v>0.0362</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3732776039260836</v>
+        <v>0.3689678494100561</v>
       </c>
       <c r="J19" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K19" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0492288381511119</v>
+        <v>0.04842249043041547</v>
       </c>
       <c r="M19" t="n">
-        <v>10.30089760263065</v>
+        <v>10.29239715770095</v>
       </c>
       <c r="N19" t="n">
-        <v>157.1195516923373</v>
+        <v>156.8398406731579</v>
       </c>
       <c r="O19" t="n">
-        <v>12.53473381019068</v>
+        <v>12.52357140248571</v>
       </c>
       <c r="P19" t="n">
-        <v>319.0972654044622</v>
+        <v>319.1397825965198</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -36938,28 +37035,28 @@
         <v>0.0408</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4872485153340488</v>
+        <v>0.4842983583730223</v>
       </c>
       <c r="J20" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K20" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L20" t="n">
-        <v>0.078921629597409</v>
+        <v>0.07850577308045803</v>
       </c>
       <c r="M20" t="n">
-        <v>10.31803723671519</v>
+        <v>10.30238706151421</v>
       </c>
       <c r="N20" t="n">
-        <v>161.7750483164845</v>
+        <v>161.3984329114151</v>
       </c>
       <c r="O20" t="n">
-        <v>12.71908205479014</v>
+        <v>12.70426829500287</v>
       </c>
       <c r="P20" t="n">
-        <v>318.9544869308266</v>
+        <v>318.9835912312329</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37016,28 +37113,28 @@
         <v>0.0379</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4861276027007098</v>
+        <v>0.484114360130164</v>
       </c>
       <c r="J21" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K21" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08308878938192543</v>
+        <v>0.08296267125223356</v>
       </c>
       <c r="M21" t="n">
-        <v>9.943303791177971</v>
+        <v>9.923956526143693</v>
       </c>
       <c r="N21" t="n">
-        <v>152.2633440052088</v>
+        <v>151.8736789303861</v>
       </c>
       <c r="O21" t="n">
-        <v>12.33950339378408</v>
+        <v>12.32370394525875</v>
       </c>
       <c r="P21" t="n">
-        <v>324.9750829757457</v>
+        <v>324.9949442974781</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37094,28 +37191,28 @@
         <v>0.0374</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5898050530950752</v>
+        <v>0.5885244562428579</v>
       </c>
       <c r="J22" t="n">
+        <v>359</v>
+      </c>
+      <c r="K22" t="n">
         <v>358</v>
       </c>
-      <c r="K22" t="n">
-        <v>357</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.1231786430590608</v>
+        <v>0.1234401334165577</v>
       </c>
       <c r="M22" t="n">
-        <v>9.871474209225466</v>
+        <v>9.848044160259782</v>
       </c>
       <c r="N22" t="n">
-        <v>144.7500368865085</v>
+        <v>144.3596843720769</v>
       </c>
       <c r="O22" t="n">
-        <v>12.03121094846685</v>
+        <v>12.01497750193802</v>
       </c>
       <c r="P22" t="n">
-        <v>333.1744071921892</v>
+        <v>333.1870456734558</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37172,28 +37269,28 @@
         <v>0.0309</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4274872198549635</v>
+        <v>0.4305881868512354</v>
       </c>
       <c r="J23" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K23" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L23" t="n">
-        <v>0.07302455463184077</v>
+        <v>0.07443851171991112</v>
       </c>
       <c r="M23" t="n">
-        <v>9.341584863555251</v>
+        <v>9.334536502982367</v>
       </c>
       <c r="N23" t="n">
-        <v>135.7710212720829</v>
+        <v>135.4728591950173</v>
       </c>
       <c r="O23" t="n">
-        <v>11.65208227194105</v>
+        <v>11.63928087104256</v>
       </c>
       <c r="P23" t="n">
-        <v>342.040337767162</v>
+        <v>342.009722748796</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -37250,28 +37347,28 @@
         <v>0.0259</v>
       </c>
       <c r="I24" t="n">
-        <v>0.527499159488106</v>
+        <v>0.5262169943909811</v>
       </c>
       <c r="J24" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K24" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L24" t="n">
-        <v>0.07559606854360934</v>
+        <v>0.07573123213586364</v>
       </c>
       <c r="M24" t="n">
-        <v>11.80679429669106</v>
+        <v>11.77875397444094</v>
       </c>
       <c r="N24" t="n">
-        <v>198.6625780821056</v>
+        <v>198.1231800898183</v>
       </c>
       <c r="O24" t="n">
-        <v>14.09477130293733</v>
+        <v>14.0756236128215</v>
       </c>
       <c r="P24" t="n">
-        <v>348.266509334022</v>
+        <v>348.2791583281772</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -37328,28 +37425,28 @@
         <v>0.0383</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6177781050087749</v>
+        <v>0.6181299676350057</v>
       </c>
       <c r="J25" t="n">
+        <v>359</v>
+      </c>
+      <c r="K25" t="n">
         <v>358</v>
       </c>
-      <c r="K25" t="n">
-        <v>357</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.1101252034105454</v>
+        <v>0.1109114845697864</v>
       </c>
       <c r="M25" t="n">
-        <v>11.1465747410789</v>
+        <v>11.11763904693469</v>
       </c>
       <c r="N25" t="n">
-        <v>180.5348919189208</v>
+        <v>180.0316608406992</v>
       </c>
       <c r="O25" t="n">
-        <v>13.43632732255808</v>
+        <v>13.41758774298492</v>
       </c>
       <c r="P25" t="n">
-        <v>345.696878221019</v>
+        <v>345.6934104038208</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -37406,28 +37503,28 @@
         <v>0.0429</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5657709030405199</v>
+        <v>0.569181363348034</v>
       </c>
       <c r="J26" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K26" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L26" t="n">
-        <v>0.09312462293518908</v>
+        <v>0.09468373268835084</v>
       </c>
       <c r="M26" t="n">
-        <v>11.08459018465095</v>
+        <v>11.07575799456136</v>
       </c>
       <c r="N26" t="n">
-        <v>182.8511951530316</v>
+        <v>182.4372188138137</v>
       </c>
       <c r="O26" t="n">
-        <v>13.52224815454263</v>
+        <v>13.50693225028591</v>
       </c>
       <c r="P26" t="n">
-        <v>343.230663683693</v>
+        <v>343.1970157808221</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -37465,7 +37562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA359"/>
+  <dimension ref="A1:AA360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86587,6 +86684,143 @@
         </is>
       </c>
     </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 21:53:04+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>-37.70870093634981,178.53462736309262</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>-37.70923575502108,178.53403328279782</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>-37.70975299811835,178.5334099767522</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>-37.71026611508861,178.5327798147786</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>-37.71083373193603,178.532240306227</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>-37.71139147440872,178.53168438096677</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>-37.711941728644966,178.53111600769856</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>-37.7125288008805,178.53061151883503</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>-37.71307758795328,178.53004687029</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>-37.713662555781106,178.5295262300431</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>-37.714244646556544,178.5289942954123</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>-37.71483165065445,178.52847444061027</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>-37.715436644496386,178.5279987817682</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>-37.71605578445681,178.52754508510537</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>-37.7166816324541,178.52709635500995</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>-37.71729937176647,178.52663381244605</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>-37.717932339502966,178.52622361024228</t>
+        </is>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>-37.71857513736897,178.5258415796617</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>-37.71922961849398,178.52550545677596</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>-37.719884457095894,178.5251707333781</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>-37.720558639620805,178.52487348293155</t>
+        </is>
+      </c>
+      <c r="W360" t="inlineStr">
+        <is>
+          <t>-37.72123341489916,178.52457510844985</t>
+        </is>
+      </c>
+      <c r="X360" t="inlineStr">
+        <is>
+          <t>-37.72186304212551,178.5241630364292</t>
+        </is>
+      </c>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>-37.72254386827058,178.52391967072518</t>
+        </is>
+      </c>
+      <c r="Z360" t="inlineStr">
+        <is>
+          <t>-37.72322703364026,178.52367561718262</t>
+        </is>
+      </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0218/nzd0218.xlsx
+++ b/data/nzd0218/nzd0218.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA360"/>
+  <dimension ref="A1:AA361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31766,6 +31766,93 @@
       <c r="AA360" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:52:58+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>366.72</v>
+      </c>
+      <c r="C361" t="n">
+        <v>363.91</v>
+      </c>
+      <c r="D361" t="n">
+        <v>357.05</v>
+      </c>
+      <c r="E361" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="F361" t="n">
+        <v>351.57</v>
+      </c>
+      <c r="G361" t="n">
+        <v>353.87</v>
+      </c>
+      <c r="H361" t="n">
+        <v>354.92</v>
+      </c>
+      <c r="I361" t="n">
+        <v>360.63</v>
+      </c>
+      <c r="J361" t="n">
+        <v>357.95</v>
+      </c>
+      <c r="K361" t="n">
+        <v>350.07</v>
+      </c>
+      <c r="L361" t="n">
+        <v>340.15</v>
+      </c>
+      <c r="M361" t="n">
+        <v>333.13</v>
+      </c>
+      <c r="N361" t="n">
+        <v>330.71</v>
+      </c>
+      <c r="O361" t="n">
+        <v>328.98</v>
+      </c>
+      <c r="P361" t="n">
+        <v>326.41</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>321.6</v>
+      </c>
+      <c r="R361" t="n">
+        <v>319.29</v>
+      </c>
+      <c r="S361" t="n">
+        <v>319.69</v>
+      </c>
+      <c r="T361" t="n">
+        <v>324.68</v>
+      </c>
+      <c r="U361" t="n">
+        <v>331.82</v>
+      </c>
+      <c r="V361" t="n">
+        <v>344.2</v>
+      </c>
+      <c r="W361" t="n">
+        <v>357.63</v>
+      </c>
+      <c r="X361" t="n">
+        <v>358.07</v>
+      </c>
+      <c r="Y361" t="n">
+        <v>361.52</v>
+      </c>
+      <c r="Z361" t="n">
+        <v>365.26</v>
+      </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -31780,7 +31867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B368"/>
+  <dimension ref="A1:B369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35463,6 +35550,16 @@
       </c>
       <c r="B368" t="n">
         <v>0.29</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -35631,28 +35728,28 @@
         <v>0.0512</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02145663805186883</v>
+        <v>-0.01101968889954341</v>
       </c>
       <c r="J2" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K2" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002067182788405564</v>
+        <v>5.452387843363216e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>8.998941142173653</v>
+        <v>9.025804625930196</v>
       </c>
       <c r="N2" t="n">
-        <v>130.538007644981</v>
+        <v>131.1002128204803</v>
       </c>
       <c r="O2" t="n">
-        <v>11.42532308711578</v>
+        <v>11.44990012272947</v>
       </c>
       <c r="P2" t="n">
-        <v>348.9648688882542</v>
+        <v>348.8614427560146</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35709,28 +35806,28 @@
         <v>0.0444</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03554563856616799</v>
+        <v>0.04626286065812223</v>
       </c>
       <c r="J3" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K3" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00044327847329384</v>
+        <v>0.0007514511913270239</v>
       </c>
       <c r="M3" t="n">
-        <v>10.38450610420712</v>
+        <v>10.40710904426312</v>
       </c>
       <c r="N3" t="n">
-        <v>167.026637976211</v>
+        <v>167.5378223341733</v>
       </c>
       <c r="O3" t="n">
-        <v>12.92387859646674</v>
+        <v>12.94364022731524</v>
       </c>
       <c r="P3" t="n">
-        <v>344.1318279058913</v>
+        <v>344.025624377145</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35787,28 +35884,28 @@
         <v>0.0371</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0708961144782764</v>
+        <v>-0.06252415621219169</v>
       </c>
       <c r="J4" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K4" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001688525848140277</v>
+        <v>0.001318364317433041</v>
       </c>
       <c r="M4" t="n">
-        <v>10.58682443354506</v>
+        <v>10.60051566146894</v>
       </c>
       <c r="N4" t="n">
-        <v>174.2149871000956</v>
+        <v>174.3261153289691</v>
       </c>
       <c r="O4" t="n">
-        <v>13.19905250766492</v>
+        <v>13.20326154133777</v>
       </c>
       <c r="P4" t="n">
-        <v>344.2426206008435</v>
+        <v>344.1596577301717</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35865,28 +35962,28 @@
         <v>0.0366</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1756134816789424</v>
+        <v>-0.1678492066671967</v>
       </c>
       <c r="J5" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K5" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009789920783186856</v>
+        <v>0.008987473276307445</v>
       </c>
       <c r="M5" t="n">
-        <v>10.59086389472946</v>
+        <v>10.59973620121179</v>
       </c>
       <c r="N5" t="n">
-        <v>182.8715589268849</v>
+        <v>182.8753909454846</v>
       </c>
       <c r="O5" t="n">
-        <v>13.52300110651792</v>
+        <v>13.52314279098925</v>
       </c>
       <c r="P5" t="n">
-        <v>341.6283735634652</v>
+        <v>341.5514325989755</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35943,28 +36040,28 @@
         <v>0.0382</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1087604889079304</v>
+        <v>-0.1016953269010374</v>
       </c>
       <c r="J6" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K6" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005003655330566015</v>
+        <v>0.004394177450307679</v>
       </c>
       <c r="M6" t="n">
-        <v>8.955646482782274</v>
+        <v>8.968089751544804</v>
       </c>
       <c r="N6" t="n">
-        <v>137.8982316652153</v>
+        <v>137.93897031931</v>
       </c>
       <c r="O6" t="n">
-        <v>11.74300777761879</v>
+        <v>11.74474224150151</v>
       </c>
       <c r="P6" t="n">
-        <v>342.0832881655678</v>
+        <v>342.0132751407505</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36021,28 +36118,28 @@
         <v>0.0418</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1540720098598392</v>
+        <v>-0.1459454744729721</v>
       </c>
       <c r="J7" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K7" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01079547328524422</v>
+        <v>0.009721581938218482</v>
       </c>
       <c r="M7" t="n">
-        <v>8.743758555054537</v>
+        <v>8.766510161217884</v>
       </c>
       <c r="N7" t="n">
-        <v>127.5187948477384</v>
+        <v>127.7252579511644</v>
       </c>
       <c r="O7" t="n">
-        <v>11.2924220098143</v>
+        <v>11.30155997865624</v>
       </c>
       <c r="P7" t="n">
-        <v>343.7265804980671</v>
+        <v>343.6460496732728</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36099,28 +36196,28 @@
         <v>0.0328</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1425090874371866</v>
+        <v>-0.1338965352002463</v>
       </c>
       <c r="J8" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K8" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008589369324087825</v>
+        <v>0.007607717713717377</v>
       </c>
       <c r="M8" t="n">
-        <v>9.252889357724872</v>
+        <v>9.273726175404839</v>
       </c>
       <c r="N8" t="n">
-        <v>137.42308963976</v>
+        <v>137.6711107159239</v>
       </c>
       <c r="O8" t="n">
-        <v>11.72275947205947</v>
+        <v>11.73333331649297</v>
       </c>
       <c r="P8" t="n">
-        <v>343.6156091020126</v>
+        <v>343.5302620380788</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36177,28 +36274,28 @@
         <v>0.0326</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08957403108083632</v>
+        <v>-0.0824987851662181</v>
       </c>
       <c r="J9" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K9" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004615973520503136</v>
+        <v>0.003928831450086268</v>
       </c>
       <c r="M9" t="n">
-        <v>7.950450494152142</v>
+        <v>7.96758650832807</v>
       </c>
       <c r="N9" t="n">
-        <v>101.674507505159</v>
+        <v>101.8174337253424</v>
       </c>
       <c r="O9" t="n">
-        <v>10.08337778252699</v>
+        <v>10.09046251295462</v>
       </c>
       <c r="P9" t="n">
-        <v>350.610106140043</v>
+        <v>350.5399384348547</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36255,28 +36352,28 @@
         <v>0.0306</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1757976454223021</v>
+        <v>-0.169511805026398</v>
       </c>
       <c r="J10" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K10" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01861091571893425</v>
+        <v>0.01738396397720887</v>
       </c>
       <c r="M10" t="n">
-        <v>8.004982360149002</v>
+        <v>8.017123771179422</v>
       </c>
       <c r="N10" t="n">
-        <v>95.76792322711023</v>
+        <v>95.83739463349303</v>
       </c>
       <c r="O10" t="n">
-        <v>9.786108686659382</v>
+        <v>9.78965753402503</v>
       </c>
       <c r="P10" t="n">
-        <v>351.6359681106474</v>
+        <v>351.5736292179668</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36333,28 +36430,28 @@
         <v>0.0306</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0792073540728068</v>
+        <v>-0.07577523570912448</v>
       </c>
       <c r="J11" t="n">
+        <v>360</v>
+      </c>
+      <c r="K11" t="n">
         <v>359</v>
       </c>
-      <c r="K11" t="n">
-        <v>358</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.004309249001914317</v>
+        <v>0.00396789597582814</v>
       </c>
       <c r="M11" t="n">
-        <v>7.486103854181492</v>
+        <v>7.482832891382808</v>
       </c>
       <c r="N11" t="n">
-        <v>85.20688776372025</v>
+        <v>85.06988179072783</v>
       </c>
       <c r="O11" t="n">
-        <v>9.230757702578931</v>
+        <v>9.223333550876703</v>
       </c>
       <c r="P11" t="n">
-        <v>346.1693015629284</v>
+        <v>346.1353234934018</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36411,28 +36508,28 @@
         <v>0.0328</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.06305559149832674</v>
+        <v>-0.06233200224959422</v>
       </c>
       <c r="J12" t="n">
+        <v>360</v>
+      </c>
+      <c r="K12" t="n">
         <v>359</v>
       </c>
-      <c r="K12" t="n">
-        <v>358</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.003479251415790752</v>
+        <v>0.00342337824092187</v>
       </c>
       <c r="M12" t="n">
-        <v>6.443409829899355</v>
+        <v>6.429413868390246</v>
       </c>
       <c r="N12" t="n">
-        <v>66.93735517996183</v>
+        <v>66.75536010147442</v>
       </c>
       <c r="O12" t="n">
-        <v>8.181525235551243</v>
+        <v>8.17039534548203</v>
       </c>
       <c r="P12" t="n">
-        <v>340.5750522775791</v>
+        <v>340.5678887234131</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36489,28 +36586,28 @@
         <v>0.0371</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06731415792549397</v>
+        <v>-0.06795023281796882</v>
       </c>
       <c r="J13" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K13" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L13" t="n">
-        <v>0.00465950419019856</v>
+        <v>0.004779937934965894</v>
       </c>
       <c r="M13" t="n">
-        <v>5.938916082615866</v>
+        <v>5.925130415031568</v>
       </c>
       <c r="N13" t="n">
-        <v>57.00749373316</v>
+        <v>56.8512693429745</v>
       </c>
       <c r="O13" t="n">
-        <v>7.550330703562593</v>
+        <v>7.539978073109662</v>
       </c>
       <c r="P13" t="n">
-        <v>336.0500125380709</v>
+        <v>336.0563165884769</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36567,28 +36664,28 @@
         <v>0.0363</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1079674362534236</v>
+        <v>-0.1085423811957636</v>
       </c>
       <c r="J14" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K14" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01132662557928177</v>
+        <v>0.01152410792116465</v>
       </c>
       <c r="M14" t="n">
-        <v>6.051778962068178</v>
+        <v>6.037767949630569</v>
       </c>
       <c r="N14" t="n">
-        <v>59.65133500069717</v>
+        <v>59.48844330400362</v>
       </c>
       <c r="O14" t="n">
-        <v>7.723427671746346</v>
+        <v>7.712875164554631</v>
       </c>
       <c r="P14" t="n">
-        <v>334.622597033082</v>
+        <v>334.6282945152455</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36645,28 +36742,28 @@
         <v>0.0343</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02764873361801335</v>
+        <v>0.0251775213590641</v>
       </c>
       <c r="J15" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K15" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0004755417730316625</v>
+        <v>0.0003968803277059063</v>
       </c>
       <c r="M15" t="n">
-        <v>7.809290386303483</v>
+        <v>7.80112723489118</v>
       </c>
       <c r="N15" t="n">
-        <v>94.19710103087425</v>
+        <v>93.98728967983855</v>
       </c>
       <c r="O15" t="n">
-        <v>9.705519101566605</v>
+        <v>9.694704207960063</v>
       </c>
       <c r="P15" t="n">
-        <v>332.5810636778893</v>
+        <v>332.6055524362569</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36723,28 +36820,28 @@
         <v>0.0361</v>
       </c>
       <c r="I16" t="n">
-        <v>0.09871635526736977</v>
+        <v>0.09468214193257375</v>
       </c>
       <c r="J16" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K16" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L16" t="n">
-        <v>0.004949408729286842</v>
+        <v>0.004580884708567101</v>
       </c>
       <c r="M16" t="n">
-        <v>8.345569233875075</v>
+        <v>8.342253883466467</v>
       </c>
       <c r="N16" t="n">
-        <v>114.8556495954663</v>
+        <v>114.6747792100298</v>
       </c>
       <c r="O16" t="n">
-        <v>10.71707280909607</v>
+        <v>10.70863106143964</v>
       </c>
       <c r="P16" t="n">
-        <v>330.8484896768323</v>
+        <v>330.8884671717648</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36801,28 +36898,28 @@
         <v>0.0362</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1937097604059312</v>
+        <v>0.1884054798209998</v>
       </c>
       <c r="J17" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K17" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01408180379747315</v>
+        <v>0.01340194132937544</v>
       </c>
       <c r="M17" t="n">
-        <v>9.694973713310461</v>
+        <v>9.694619720329918</v>
       </c>
       <c r="N17" t="n">
-        <v>154.0167293857898</v>
+        <v>153.8277735446868</v>
       </c>
       <c r="O17" t="n">
-        <v>12.41034767384821</v>
+        <v>12.40273250314973</v>
       </c>
       <c r="P17" t="n">
-        <v>325.7143861022102</v>
+        <v>325.7669494727131</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36879,28 +36976,28 @@
         <v>0.0329</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3145881562638008</v>
+        <v>0.3088278203890699</v>
       </c>
       <c r="J18" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K18" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03419206585180645</v>
+        <v>0.03315820525889657</v>
       </c>
       <c r="M18" t="n">
-        <v>10.48764905176293</v>
+        <v>10.48660638567918</v>
       </c>
       <c r="N18" t="n">
-        <v>163.8824543701753</v>
+        <v>163.7089347371804</v>
       </c>
       <c r="O18" t="n">
-        <v>12.80165826641905</v>
+        <v>12.79487923886663</v>
       </c>
       <c r="P18" t="n">
-        <v>320.9607415390723</v>
+        <v>321.0178242412326</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -36957,28 +37054,28 @@
         <v>0.0362</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3689678494100561</v>
+        <v>0.363639270971991</v>
       </c>
       <c r="J19" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K19" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L19" t="n">
-        <v>0.04842249043041547</v>
+        <v>0.04734095447024478</v>
       </c>
       <c r="M19" t="n">
-        <v>10.29239715770095</v>
+        <v>10.28848407180487</v>
       </c>
       <c r="N19" t="n">
-        <v>156.8398406731579</v>
+        <v>156.6452362858247</v>
       </c>
       <c r="O19" t="n">
-        <v>12.52357140248571</v>
+        <v>12.51579946650731</v>
       </c>
       <c r="P19" t="n">
-        <v>319.1397825965198</v>
+        <v>319.1925867493561</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -37035,28 +37132,28 @@
         <v>0.0408</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4842983583730223</v>
+        <v>0.4801375432885924</v>
       </c>
       <c r="J20" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K20" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L20" t="n">
-        <v>0.07850577308045803</v>
+        <v>0.07769504793135851</v>
       </c>
       <c r="M20" t="n">
-        <v>10.30238706151421</v>
+        <v>10.2924577305054</v>
       </c>
       <c r="N20" t="n">
-        <v>161.3984329114151</v>
+        <v>161.0970853940224</v>
       </c>
       <c r="O20" t="n">
-        <v>12.70426829500287</v>
+        <v>12.69240266435092</v>
       </c>
       <c r="P20" t="n">
-        <v>318.9835912312329</v>
+        <v>319.0248233005729</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -37113,28 +37210,28 @@
         <v>0.0379</v>
       </c>
       <c r="I21" t="n">
-        <v>0.484114360130164</v>
+        <v>0.4806013525486827</v>
       </c>
       <c r="J21" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K21" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08296267125223356</v>
+        <v>0.08232978037975291</v>
       </c>
       <c r="M21" t="n">
-        <v>9.923956526143693</v>
+        <v>9.910769419894036</v>
       </c>
       <c r="N21" t="n">
-        <v>151.8736789303861</v>
+        <v>151.5565841053936</v>
       </c>
       <c r="O21" t="n">
-        <v>12.32370394525875</v>
+        <v>12.31083198266444</v>
       </c>
       <c r="P21" t="n">
-        <v>324.9949442974781</v>
+        <v>325.0297568448402</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -37191,28 +37288,28 @@
         <v>0.0374</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5885244562428579</v>
+        <v>0.5857954768124171</v>
       </c>
       <c r="J22" t="n">
+        <v>360</v>
+      </c>
+      <c r="K22" t="n">
         <v>359</v>
       </c>
-      <c r="K22" t="n">
-        <v>358</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.1234401334165577</v>
+        <v>0.1231338960682501</v>
       </c>
       <c r="M22" t="n">
-        <v>9.848044160259782</v>
+        <v>9.829302879026072</v>
       </c>
       <c r="N22" t="n">
-        <v>144.3596843720769</v>
+        <v>144.0209375616183</v>
       </c>
       <c r="O22" t="n">
-        <v>12.01497750193802</v>
+        <v>12.00087236669144</v>
       </c>
       <c r="P22" t="n">
-        <v>333.1870456734558</v>
+        <v>333.2140998404797</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -37269,28 +37366,28 @@
         <v>0.0309</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4305881868512354</v>
+        <v>0.4329004631119723</v>
       </c>
       <c r="J23" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K23" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L23" t="n">
-        <v>0.07443851171991112</v>
+        <v>0.07563706051976871</v>
       </c>
       <c r="M23" t="n">
-        <v>9.334536502982367</v>
+        <v>9.322569035038612</v>
       </c>
       <c r="N23" t="n">
-        <v>135.4728591950173</v>
+        <v>135.1400424919167</v>
       </c>
       <c r="O23" t="n">
-        <v>11.63928087104256</v>
+        <v>11.62497494586189</v>
       </c>
       <c r="P23" t="n">
-        <v>342.009722748796</v>
+        <v>341.9867910908812</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -37347,28 +37444,28 @@
         <v>0.0259</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5262169943909811</v>
+        <v>0.5237453319427837</v>
       </c>
       <c r="J24" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K24" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L24" t="n">
-        <v>0.07573123213586364</v>
+        <v>0.07553765101979648</v>
       </c>
       <c r="M24" t="n">
-        <v>11.77875397444094</v>
+        <v>11.75525212505103</v>
       </c>
       <c r="N24" t="n">
-        <v>198.1231800898183</v>
+        <v>197.6247040779506</v>
       </c>
       <c r="O24" t="n">
-        <v>14.0756236128215</v>
+        <v>14.05790539440178</v>
       </c>
       <c r="P24" t="n">
-        <v>348.2791583281772</v>
+        <v>348.3036515477463</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -37425,28 +37522,28 @@
         <v>0.0383</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6181299676350057</v>
+        <v>0.6176913728756979</v>
       </c>
       <c r="J25" t="n">
+        <v>360</v>
+      </c>
+      <c r="K25" t="n">
         <v>359</v>
       </c>
-      <c r="K25" t="n">
-        <v>358</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.1109114845697864</v>
+        <v>0.1114526492985494</v>
       </c>
       <c r="M25" t="n">
-        <v>11.11763904693469</v>
+        <v>11.08820888636518</v>
       </c>
       <c r="N25" t="n">
-        <v>180.0316608406992</v>
+        <v>179.5318184901201</v>
       </c>
       <c r="O25" t="n">
-        <v>13.41758774298492</v>
+        <v>13.39894840986113</v>
       </c>
       <c r="P25" t="n">
-        <v>345.6934104038208</v>
+        <v>345.6977525044265</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -37503,28 +37600,28 @@
         <v>0.0429</v>
       </c>
       <c r="I26" t="n">
-        <v>0.569181363348034</v>
+        <v>0.573041986208882</v>
       </c>
       <c r="J26" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K26" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L26" t="n">
-        <v>0.09468373268835084</v>
+        <v>0.09638677233399129</v>
       </c>
       <c r="M26" t="n">
-        <v>11.07575799456136</v>
+        <v>11.06971160267853</v>
       </c>
       <c r="N26" t="n">
-        <v>182.4372188138137</v>
+        <v>182.053667491492</v>
       </c>
       <c r="O26" t="n">
-        <v>13.50693225028591</v>
+        <v>13.49272646619252</v>
       </c>
       <c r="P26" t="n">
-        <v>343.1970157808221</v>
+        <v>343.1587536808693</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -37562,7 +37659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA360"/>
+  <dimension ref="A1:AA361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86821,6 +86918,143 @@
         </is>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:52:58+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>-37.708698007824495,178.53462249222466</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>-37.70923212146043,178.53402723928303</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>-37.709744266673695,178.5333954542107</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-37.7102583597833,178.53276691581732</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>-37.7108132318005,178.5322062094762</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-37.711375041681436,178.53165704928836</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-37.71193006840065,178.53109661382632</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-37.71250963800467,178.5305780064597</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>-37.7130633448775,178.53001673053816</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>-37.71364976666442,178.52949481954295</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>-37.714228291122765,178.52895412594972</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>-37.71481869738909,178.52844262698454</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>-37.71542795427991,178.52797743829433</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>-37.716044427923094,178.5275158071037</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>-37.716673749167775,178.52707439612087</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>-37.717297816874584,178.5266293588729</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>-37.717928289529,178.52621201014549</t>
+        </is>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>-37.718568556128844,178.5258227293499</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>-37.71922167188137,178.5254835332892</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>-37.719874292130044,178.52514399584567</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>-37.72054885307131,178.5248480225793</t>
+        </is>
+      </c>
+      <c r="W361" t="inlineStr">
+        <is>
+          <t>-37.72122840417577,178.52456207263148</t>
+        </is>
+      </c>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>-37.72185656329991,178.52414132405607</t>
+        </is>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>-37.722540800894436,178.52390524390574</t>
+        </is>
+      </c>
+      <c r="Z361" t="inlineStr">
+        <is>
+          <t>-37.7232290979648,178.523685579776</t>
+        </is>
+      </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
